--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126279522</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126279620</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126279534</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>126279646</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126279534</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>126279646</v>
       </c>
       <c r="B5" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126279522</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126279620</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126279534</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>126279646</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1074,6 +1074,6222 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129465376</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497292</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6832709</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129476418</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79662</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497415</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6832767</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129476453</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>497266</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6832713</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129464751</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90575</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497356</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6832723</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129467135</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497389</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6832791</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129476442</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78800</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>497337</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6832676</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129465572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>497254</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6832729</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129476419</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79633</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>497336</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6832679</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129476462</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78709</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>353</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>497254</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6832752</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129476423</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97331</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497256</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6832740</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129476464</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78709</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>353</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497336</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6832724</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129476427</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>497307</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6832769</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129476426</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97331</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>497413</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6832724</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129476428</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92829</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>497387</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6832781</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129476457</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>497355</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6832689</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129476449</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>497318</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6832776</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129464182</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>497410</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6832744</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129476429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>497288</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6832771</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129476437</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>497395</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6832737</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129464639</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>497352</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6832732</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129476446</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91716</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>497331</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6832758</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129476454</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>497292</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6832702</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129476417</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79662</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>497430</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6832760</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129464293</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78709</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>353</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>497396</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6832740</v>
+      </c>
+      <c r="S29" t="n">
+        <v>12</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129476430</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>497250</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6832730</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129476416</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79662</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>497395</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6832737</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129476450</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>497272</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6832783</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129476466</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92825</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>497385</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6832779</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129476451</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>497241</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6832763</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129476452</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>497258</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6832721</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129476435</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>497301</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6832764</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129476438</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>497401</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6832738</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129476459</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>497362</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6832731</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129476455</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>497307</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6832696</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129476436</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>497334</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6832674</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129465773</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>497256</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6832783</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129464008</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>497425</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6832750</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129476443</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78800</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>497393</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6832735</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129465323</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>497290</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6832699</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129476421</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90575</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>497336</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6832758</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129476422</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90575</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>497310</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6832692</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129476424</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97331</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>497389</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6832716</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129476433</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91596</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>497349</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6832759</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129476415</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79662</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>497337</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6832679</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129476460</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>497427</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6832743</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129476463</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78709</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>353</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>497356</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6832686</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129476461</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78709</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>353</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>497297</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6832767</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129476456</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>497344</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6832689</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129476434</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91596</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>497367</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6832720</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129476439</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>497415</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6832767</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129476465</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78709</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>353</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>497434</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6832759</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129464078</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>497426</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6832743</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129463331</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58162</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>497447</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6832767</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129466317</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>497335</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6832765</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129476447</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>497367</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6832744</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129476448</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>497361</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6832760</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129476458</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>497334</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6832718</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129465171</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>497309</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6832672</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129476432</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91596</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>497389</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6832749</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129466545</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>497366</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6832752</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129465586</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>497254</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6832729</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129464850</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>497345</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6832696</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129476431</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92186</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>483</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rostskinn</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Crustoderma dryinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>497392</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6832754</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129476420</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79633</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>497431</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6832752</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129465376</v>
+        <v>129476418</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497292</v>
+        <v>497415</v>
       </c>
       <c r="R6" t="n">
-        <v>6832709</v>
+        <v>6832767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,22 +1161,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476418</v>
+        <v>129465376</v>
       </c>
       <c r="B7" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,34 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497415</v>
+        <v>497292</v>
       </c>
       <c r="R7" t="n">
-        <v>6832767</v>
+        <v>6832709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,12 +1258,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
         <v>129476453</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129464751</v>
+        <v>129467135</v>
       </c>
       <c r="B9" t="n">
-        <v>90575</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497356</v>
+        <v>497389</v>
       </c>
       <c r="R9" t="n">
-        <v>6832723</v>
+        <v>6832791</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129467135</v>
+        <v>129476442</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497389</v>
+        <v>497337</v>
       </c>
       <c r="R10" t="n">
-        <v>6832791</v>
+        <v>6832676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B11" t="n">
-        <v>78800</v>
+        <v>90577</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,22 +1646,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129465572</v>
+        <v>129476427</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,34 +1669,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497254</v>
+        <v>497307</v>
       </c>
       <c r="R12" t="n">
-        <v>6832729</v>
+        <v>6832769</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,22 +1751,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476419</v>
+        <v>129476464</v>
       </c>
       <c r="B13" t="n">
-        <v>79633</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1774,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,7 +1801,7 @@
         <v>497336</v>
       </c>
       <c r="R13" t="n">
-        <v>6832679</v>
+        <v>6832724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,32 +1860,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476462</v>
+        <v>129476428</v>
       </c>
       <c r="B14" t="n">
-        <v>78709</v>
+        <v>92831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1895,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497254</v>
+        <v>497387</v>
       </c>
       <c r="R14" t="n">
-        <v>6832752</v>
+        <v>6832781</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476423</v>
+        <v>129476426</v>
       </c>
       <c r="B15" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497256</v>
+        <v>497413</v>
       </c>
       <c r="R15" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476464</v>
+        <v>129476462</v>
       </c>
       <c r="B16" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497336</v>
+        <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832724</v>
+        <v>6832752</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,53 +2151,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476427</v>
+        <v>129476423</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>97333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497307</v>
+        <v>497256</v>
       </c>
       <c r="R17" t="n">
-        <v>6832769</v>
+        <v>6832740</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,45 +2248,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476426</v>
+        <v>129465572</v>
       </c>
       <c r="B18" t="n">
-        <v>97331</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497413</v>
+        <v>497254</v>
       </c>
       <c r="R18" t="n">
-        <v>6832724</v>
+        <v>6832729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,44 +2333,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476428</v>
+        <v>129476419</v>
       </c>
       <c r="B19" t="n">
-        <v>92829</v>
+        <v>79634</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497387</v>
+        <v>497336</v>
       </c>
       <c r="R19" t="n">
-        <v>6832781</v>
+        <v>6832679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476457</v>
+        <v>129476449</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497355</v>
+        <v>497318</v>
       </c>
       <c r="R20" t="n">
-        <v>6832689</v>
+        <v>6832776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476449</v>
+        <v>129476457</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497318</v>
+        <v>497355</v>
       </c>
       <c r="R21" t="n">
-        <v>6832776</v>
+        <v>6832689</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129464182</v>
+        <v>129476429</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497410</v>
+        <v>497288</v>
       </c>
       <c r="R22" t="n">
-        <v>6832744</v>
+        <v>6832771</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476429</v>
+        <v>129464182</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497288</v>
+        <v>497410</v>
       </c>
       <c r="R23" t="n">
-        <v>6832771</v>
+        <v>6832744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,12 +2818,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
         <v>129476437</v>
       </c>
       <c r="B24" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129464639</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476446</v>
+        <v>129476417</v>
       </c>
       <c r="B26" t="n">
-        <v>91716</v>
+        <v>79663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497331</v>
+        <v>497430</v>
       </c>
       <c r="R26" t="n">
-        <v>6832758</v>
+        <v>6832760</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476454</v>
+        <v>129476446</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>91718</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497292</v>
+        <v>497331</v>
       </c>
       <c r="R27" t="n">
-        <v>6832702</v>
+        <v>6832758</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476417</v>
+        <v>129476454</v>
       </c>
       <c r="B28" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497430</v>
+        <v>497292</v>
       </c>
       <c r="R28" t="n">
-        <v>6832760</v>
+        <v>6832702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129464293</v>
+        <v>129476450</v>
       </c>
       <c r="B29" t="n">
-        <v>78709</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497396</v>
+        <v>497272</v>
       </c>
       <c r="R29" t="n">
-        <v>6832740</v>
+        <v>6832783</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476430</v>
+        <v>129464293</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>78710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,37 +3423,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497250</v>
+        <v>497396</v>
       </c>
       <c r="R30" t="n">
-        <v>6832730</v>
+        <v>6832740</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3497,22 +3497,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476416</v>
+        <v>129476430</v>
       </c>
       <c r="B31" t="n">
-        <v>79662</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497395</v>
+        <v>497250</v>
       </c>
       <c r="R31" t="n">
-        <v>6832737</v>
+        <v>6832730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476450</v>
+        <v>129476416</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497272</v>
+        <v>497395</v>
       </c>
       <c r="R32" t="n">
-        <v>6832783</v>
+        <v>6832737</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476466</v>
+        <v>129476451</v>
       </c>
       <c r="B33" t="n">
-        <v>92825</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497385</v>
+        <v>497241</v>
       </c>
       <c r="R33" t="n">
-        <v>6832779</v>
+        <v>6832763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476451</v>
+        <v>129476452</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497241</v>
+        <v>497258</v>
       </c>
       <c r="R34" t="n">
-        <v>6832763</v>
+        <v>6832721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476452</v>
+        <v>129476435</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>78802</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497258</v>
+        <v>497301</v>
       </c>
       <c r="R35" t="n">
-        <v>6832721</v>
+        <v>6832764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476435</v>
+        <v>129476466</v>
       </c>
       <c r="B36" t="n">
-        <v>78801</v>
+        <v>92827</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497301</v>
+        <v>497385</v>
       </c>
       <c r="R36" t="n">
-        <v>6832764</v>
+        <v>6832779</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4094,7 +4094,7 @@
         <v>129476438</v>
       </c>
       <c r="B37" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>129476459</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>129476455</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129476436</v>
       </c>
       <c r="B40" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129465773</v>
+        <v>129464008</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497256</v>
+        <v>497425</v>
       </c>
       <c r="R41" t="n">
-        <v>6832783</v>
+        <v>6832750</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>78801</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R42" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,22 +4661,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476443</v>
+        <v>129465773</v>
       </c>
       <c r="B43" t="n">
-        <v>78800</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4684,34 +4684,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497393</v>
+        <v>497256</v>
       </c>
       <c r="R43" t="n">
-        <v>6832735</v>
+        <v>6832783</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4758,22 +4758,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129465323</v>
+        <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>90577</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497290</v>
+        <v>497336</v>
       </c>
       <c r="R44" t="n">
-        <v>6832699</v>
+        <v>6832758</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,22 +4855,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476421</v>
+        <v>129476422</v>
       </c>
       <c r="B45" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497336</v>
+        <v>497310</v>
       </c>
       <c r="R45" t="n">
-        <v>6832758</v>
+        <v>6832692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476422</v>
+        <v>129476424</v>
       </c>
       <c r="B46" t="n">
-        <v>90575</v>
+        <v>97333</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497310</v>
+        <v>497389</v>
       </c>
       <c r="R46" t="n">
-        <v>6832692</v>
+        <v>6832716</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476424</v>
+        <v>129476433</v>
       </c>
       <c r="B47" t="n">
-        <v>97331</v>
+        <v>91598</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2569</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497389</v>
+        <v>497349</v>
       </c>
       <c r="R47" t="n">
-        <v>6832716</v>
+        <v>6832759</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476433</v>
+        <v>129465323</v>
       </c>
       <c r="B48" t="n">
-        <v>91596</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497349</v>
+        <v>497290</v>
       </c>
       <c r="R48" t="n">
-        <v>6832759</v>
+        <v>6832699</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
         <v>129476415</v>
       </c>
       <c r="B49" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>129476460</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B51" t="n">
-        <v>78709</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R51" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5549,7 +5549,7 @@
         <v>129476461</v>
       </c>
       <c r="B52" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R53" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476434</v>
+        <v>129464078</v>
       </c>
       <c r="B54" t="n">
-        <v>91596</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497367</v>
+        <v>497426</v>
       </c>
       <c r="R54" t="n">
-        <v>6832720</v>
+        <v>6832743</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5825,22 +5825,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476439</v>
+        <v>129466317</v>
       </c>
       <c r="B55" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,34 +5848,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497415</v>
+        <v>497335</v>
       </c>
       <c r="R55" t="n">
-        <v>6832767</v>
+        <v>6832765</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476465</v>
+        <v>129476439</v>
       </c>
       <c r="B56" t="n">
-        <v>78709</v>
+        <v>78802</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,21 +5945,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497434</v>
+        <v>497415</v>
       </c>
       <c r="R56" t="n">
-        <v>6832759</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129464078</v>
+        <v>129476465</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>78710</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,34 +6042,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497426</v>
+        <v>497434</v>
       </c>
       <c r="R57" t="n">
-        <v>6832743</v>
+        <v>6832759</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6116,22 +6116,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129463331</v>
+        <v>129476434</v>
       </c>
       <c r="B58" t="n">
-        <v>58162</v>
+        <v>91598</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102999</v>
+        <v>2079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497447</v>
+        <v>497367</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6832720</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6213,22 +6213,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129466317</v>
+        <v>129463331</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>58162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,21 +6236,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>102999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6260,13 +6260,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497335</v>
+        <v>497447</v>
       </c>
       <c r="R59" t="n">
-        <v>6832765</v>
+        <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476447</v>
+        <v>129476448</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497367</v>
+        <v>497361</v>
       </c>
       <c r="R60" t="n">
-        <v>6832744</v>
+        <v>6832760</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476448</v>
+        <v>129476458</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497361</v>
+        <v>497334</v>
       </c>
       <c r="R61" t="n">
-        <v>6832760</v>
+        <v>6832718</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476458</v>
+        <v>129476447</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497334</v>
+        <v>497367</v>
       </c>
       <c r="R62" t="n">
-        <v>6832718</v>
+        <v>6832744</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129465171</v>
+        <v>129476432</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
+        <v>91598</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497309</v>
+        <v>497389</v>
       </c>
       <c r="R63" t="n">
-        <v>6832672</v>
+        <v>6832749</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,22 +6698,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129476432</v>
+        <v>129466545</v>
       </c>
       <c r="B64" t="n">
-        <v>91596</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6721,34 +6721,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497389</v>
+        <v>497366</v>
       </c>
       <c r="R64" t="n">
-        <v>6832749</v>
+        <v>6832752</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6795,22 +6795,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129466545</v>
+        <v>129465171</v>
       </c>
       <c r="B65" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497366</v>
+        <v>497309</v>
       </c>
       <c r="R65" t="n">
-        <v>6832752</v>
+        <v>6832672</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6904,45 +6904,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129465586</v>
+        <v>129476431</v>
       </c>
       <c r="B66" t="n">
-        <v>57887</v>
+        <v>92188</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>483</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497254</v>
+        <v>497392</v>
       </c>
       <c r="R66" t="n">
-        <v>6832729</v>
+        <v>6832754</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,12 +6989,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7004,7 +7004,7 @@
         <v>129464850</v>
       </c>
       <c r="B67" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,45 +7098,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476431</v>
+        <v>129465586</v>
       </c>
       <c r="B68" t="n">
-        <v>92186</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>483</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497392</v>
+        <v>497254</v>
       </c>
       <c r="R68" t="n">
-        <v>6832754</v>
+        <v>6832729</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,12 +7183,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
         <v>129476420</v>
       </c>
       <c r="B69" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129476418</v>
+        <v>129465376</v>
       </c>
       <c r="B6" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497415</v>
+        <v>497292</v>
       </c>
       <c r="R6" t="n">
-        <v>6832767</v>
+        <v>6832709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1161,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R7" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476453</v>
+        <v>129476418</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497266</v>
+        <v>497415</v>
       </c>
       <c r="R8" t="n">
-        <v>6832713</v>
+        <v>6832767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>90581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R10" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>90577</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R11" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,22 +1646,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476427</v>
+        <v>129476464</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,42 +1669,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497307</v>
+        <v>497336</v>
       </c>
       <c r="R12" t="n">
-        <v>6832769</v>
+        <v>6832724</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,7 +1755,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476464</v>
+        <v>129476462</v>
       </c>
       <c r="B13" t="n">
         <v>78710</v>
@@ -1798,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497336</v>
+        <v>497254</v>
       </c>
       <c r="R13" t="n">
-        <v>6832724</v>
+        <v>6832752</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1860,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476428</v>
+        <v>129476426</v>
       </c>
       <c r="B14" t="n">
-        <v>92831</v>
+        <v>97337</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1895,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497387</v>
+        <v>497413</v>
       </c>
       <c r="R14" t="n">
-        <v>6832781</v>
+        <v>6832724</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,32 +1949,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476426</v>
+        <v>129476428</v>
       </c>
       <c r="B15" t="n">
-        <v>97333</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497413</v>
+        <v>497387</v>
       </c>
       <c r="R15" t="n">
-        <v>6832724</v>
+        <v>6832781</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476462</v>
+        <v>129465572</v>
       </c>
       <c r="B16" t="n">
-        <v>78710</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,34 +2057,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832752</v>
+        <v>6832729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,57 +2131,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476423</v>
+        <v>129476427</v>
       </c>
       <c r="B17" t="n">
-        <v>97333</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497256</v>
+        <v>497307</v>
       </c>
       <c r="R17" t="n">
-        <v>6832740</v>
+        <v>6832769</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129465572</v>
+        <v>129476419</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>79634</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2259,34 +2259,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R18" t="n">
-        <v>6832729</v>
+        <v>6832679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,44 +2333,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476419</v>
+        <v>129476423</v>
       </c>
       <c r="B19" t="n">
-        <v>79634</v>
+        <v>97337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497336</v>
+        <v>497256</v>
       </c>
       <c r="R19" t="n">
-        <v>6832679</v>
+        <v>6832740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2927,45 +2927,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129464639</v>
+        <v>129476446</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497352</v>
+        <v>497331</v>
       </c>
       <c r="R25" t="n">
-        <v>6832732</v>
+        <v>6832758</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,12 +3012,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3121,45 +3121,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476446</v>
+        <v>129464639</v>
       </c>
       <c r="B27" t="n">
-        <v>91718</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497331</v>
+        <v>497352</v>
       </c>
       <c r="R27" t="n">
-        <v>6832758</v>
+        <v>6832732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,12 +3206,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476450</v>
+        <v>129464293</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497272</v>
+        <v>497396</v>
       </c>
       <c r="R29" t="n">
-        <v>6832783</v>
+        <v>6832740</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129464293</v>
+        <v>129476416</v>
       </c>
       <c r="B30" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,37 +3423,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497396</v>
+        <v>497395</v>
       </c>
       <c r="R30" t="n">
-        <v>6832740</v>
+        <v>6832737</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3497,22 +3497,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476430</v>
+        <v>129476450</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497250</v>
+        <v>497272</v>
       </c>
       <c r="R31" t="n">
-        <v>6832730</v>
+        <v>6832783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476416</v>
+        <v>129476430</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497395</v>
+        <v>497250</v>
       </c>
       <c r="R32" t="n">
-        <v>6832737</v>
+        <v>6832730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476435</v>
+        <v>129476466</v>
       </c>
       <c r="B35" t="n">
-        <v>78802</v>
+        <v>92831</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497301</v>
+        <v>497385</v>
       </c>
       <c r="R35" t="n">
-        <v>6832764</v>
+        <v>6832779</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476466</v>
+        <v>129476435</v>
       </c>
       <c r="B36" t="n">
-        <v>92827</v>
+        <v>78802</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497385</v>
+        <v>497301</v>
       </c>
       <c r="R36" t="n">
-        <v>6832779</v>
+        <v>6832764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B37" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R37" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R38" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476443</v>
+        <v>129465773</v>
       </c>
       <c r="B42" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497393</v>
+        <v>497256</v>
       </c>
       <c r="R42" t="n">
-        <v>6832735</v>
+        <v>6832783</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,22 +4661,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129465773</v>
+        <v>129476443</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4684,34 +4684,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497256</v>
+        <v>497393</v>
       </c>
       <c r="R43" t="n">
-        <v>6832783</v>
+        <v>6832735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4758,12 +4758,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
         <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129476422</v>
       </c>
       <c r="B45" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>129476424</v>
       </c>
       <c r="B46" t="n">
-        <v>97333</v>
+        <v>97337</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>129476433</v>
       </c>
       <c r="B47" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476460</v>
+        <v>129476461</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497427</v>
+        <v>497297</v>
       </c>
       <c r="R50" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R51" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R52" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R53" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129464078</v>
+        <v>129476439</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497426</v>
+        <v>497415</v>
       </c>
       <c r="R54" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5825,22 +5825,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129466317</v>
+        <v>129476465</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,34 +5848,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497335</v>
+        <v>497434</v>
       </c>
       <c r="R55" t="n">
-        <v>6832765</v>
+        <v>6832759</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476439</v>
+        <v>129464078</v>
       </c>
       <c r="B56" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,34 +5945,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497415</v>
+        <v>497426</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6019,22 +6019,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476465</v>
+        <v>129466317</v>
       </c>
       <c r="B57" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,34 +6042,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497434</v>
+        <v>497335</v>
       </c>
       <c r="R57" t="n">
-        <v>6832759</v>
+        <v>6832765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6116,12 +6116,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
         <v>129476434</v>
       </c>
       <c r="B58" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>129476432</v>
       </c>
       <c r="B63" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6904,45 +6904,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129476431</v>
+        <v>129464850</v>
       </c>
       <c r="B66" t="n">
-        <v>92188</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497392</v>
+        <v>497345</v>
       </c>
       <c r="R66" t="n">
-        <v>6832754</v>
+        <v>6832696</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,22 +6989,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464850</v>
+        <v>129465586</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497345</v>
+        <v>497254</v>
       </c>
       <c r="R67" t="n">
-        <v>6832696</v>
+        <v>6832729</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129465586</v>
+        <v>129476420</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>79634</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7109,34 +7109,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497254</v>
+        <v>497431</v>
       </c>
       <c r="R68" t="n">
-        <v>6832729</v>
+        <v>6832752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,44 +7183,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129476420</v>
+        <v>129476431</v>
       </c>
       <c r="B69" t="n">
-        <v>79634</v>
+        <v>92192</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>483</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497431</v>
+        <v>497392</v>
       </c>
       <c r="R69" t="n">
-        <v>6832752</v>
+        <v>6832754</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129467135</v>
+        <v>129464751</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>90582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497389</v>
+        <v>497356</v>
       </c>
       <c r="R9" t="n">
-        <v>6832791</v>
+        <v>6832723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B10" t="n">
-        <v>90581</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R10" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129467135</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497389</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832791</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,12 +1646,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
         <v>129476426</v>
       </c>
       <c r="B14" t="n">
-        <v>97337</v>
+        <v>97345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,32 +1949,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476428</v>
+        <v>129476423</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>97345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497387</v>
+        <v>497256</v>
       </c>
       <c r="R15" t="n">
-        <v>6832781</v>
+        <v>6832740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129465572</v>
+        <v>129476427</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,34 +2057,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497254</v>
+        <v>497307</v>
       </c>
       <c r="R16" t="n">
-        <v>6832729</v>
+        <v>6832769</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2131,65 +2139,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476427</v>
+        <v>129476428</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>92836</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497307</v>
+        <v>497387</v>
       </c>
       <c r="R17" t="n">
-        <v>6832769</v>
+        <v>6832781</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476419</v>
+        <v>129465572</v>
       </c>
       <c r="B18" t="n">
-        <v>79634</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2259,34 +2259,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497336</v>
+        <v>497254</v>
       </c>
       <c r="R18" t="n">
-        <v>6832679</v>
+        <v>6832729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,44 +2333,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476423</v>
+        <v>129476419</v>
       </c>
       <c r="B19" t="n">
-        <v>97337</v>
+        <v>79634</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497256</v>
+        <v>497336</v>
       </c>
       <c r="R19" t="n">
-        <v>6832740</v>
+        <v>6832679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2927,32 +2927,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476446</v>
+        <v>129476417</v>
       </c>
       <c r="B25" t="n">
-        <v>91722</v>
+        <v>79663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497331</v>
+        <v>497430</v>
       </c>
       <c r="R25" t="n">
-        <v>6832758</v>
+        <v>6832760</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476417</v>
+        <v>129476446</v>
       </c>
       <c r="B26" t="n">
-        <v>79663</v>
+        <v>91723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497430</v>
+        <v>497331</v>
       </c>
       <c r="R26" t="n">
-        <v>6832760</v>
+        <v>6832758</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129464293</v>
+        <v>129476430</v>
       </c>
       <c r="B29" t="n">
-        <v>78710</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497396</v>
+        <v>497250</v>
       </c>
       <c r="R29" t="n">
-        <v>6832740</v>
+        <v>6832730</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476416</v>
+        <v>129476450</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497395</v>
+        <v>497272</v>
       </c>
       <c r="R30" t="n">
-        <v>6832737</v>
+        <v>6832783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476450</v>
+        <v>129464293</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,37 +3520,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497272</v>
+        <v>497396</v>
       </c>
       <c r="R31" t="n">
-        <v>6832783</v>
+        <v>6832740</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3594,22 +3594,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476430</v>
+        <v>129476416</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497250</v>
+        <v>497395</v>
       </c>
       <c r="R32" t="n">
-        <v>6832730</v>
+        <v>6832737</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476451</v>
+        <v>129476466</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497241</v>
+        <v>497385</v>
       </c>
       <c r="R33" t="n">
-        <v>6832763</v>
+        <v>6832779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476452</v>
+        <v>129476451</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497258</v>
+        <v>497241</v>
       </c>
       <c r="R34" t="n">
-        <v>6832721</v>
+        <v>6832763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476466</v>
+        <v>129476452</v>
       </c>
       <c r="B35" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497385</v>
+        <v>497258</v>
       </c>
       <c r="R35" t="n">
-        <v>6832779</v>
+        <v>6832721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R41" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,19 +4564,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129465773</v>
+        <v>129464008</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497256</v>
+        <v>497425</v>
       </c>
       <c r="R42" t="n">
-        <v>6832783</v>
+        <v>6832750</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476443</v>
+        <v>129465773</v>
       </c>
       <c r="B43" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4684,34 +4684,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497393</v>
+        <v>497256</v>
       </c>
       <c r="R43" t="n">
-        <v>6832735</v>
+        <v>6832783</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4758,12 +4758,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
         <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129476422</v>
       </c>
       <c r="B45" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>129476424</v>
       </c>
       <c r="B46" t="n">
-        <v>97337</v>
+        <v>97345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>129476433</v>
       </c>
       <c r="B47" t="n">
-        <v>91602</v>
+        <v>91603</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476439</v>
+        <v>129476465</v>
       </c>
       <c r="B54" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497415</v>
+        <v>497434</v>
       </c>
       <c r="R54" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476465</v>
+        <v>129476434</v>
       </c>
       <c r="B55" t="n">
-        <v>78710</v>
+        <v>91603</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497434</v>
+        <v>497367</v>
       </c>
       <c r="R55" t="n">
-        <v>6832759</v>
+        <v>6832720</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129464078</v>
+        <v>129476439</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,34 +5945,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497426</v>
+        <v>497415</v>
       </c>
       <c r="R56" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6019,19 +6019,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129466317</v>
+        <v>129464078</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497335</v>
+        <v>497426</v>
       </c>
       <c r="R57" t="n">
-        <v>6832765</v>
+        <v>6832743</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476434</v>
+        <v>129466317</v>
       </c>
       <c r="B58" t="n">
-        <v>91602</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497367</v>
+        <v>497335</v>
       </c>
       <c r="R58" t="n">
-        <v>6832720</v>
+        <v>6832765</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6213,12 +6213,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476448</v>
+        <v>129476458</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497361</v>
+        <v>497334</v>
       </c>
       <c r="R60" t="n">
-        <v>6832760</v>
+        <v>6832718</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476458</v>
+        <v>129476448</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497334</v>
+        <v>497361</v>
       </c>
       <c r="R61" t="n">
-        <v>6832718</v>
+        <v>6832760</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6616,7 +6616,7 @@
         <v>129476432</v>
       </c>
       <c r="B63" t="n">
-        <v>91602</v>
+        <v>91603</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6904,10 +6904,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464850</v>
+        <v>129465586</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6915,21 +6915,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497345</v>
+        <v>497254</v>
       </c>
       <c r="R66" t="n">
-        <v>6832696</v>
+        <v>6832729</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129465586</v>
+        <v>129476420</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79634</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497254</v>
+        <v>497431</v>
       </c>
       <c r="R67" t="n">
-        <v>6832729</v>
+        <v>6832752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,44 +7086,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476420</v>
+        <v>129476431</v>
       </c>
       <c r="B68" t="n">
-        <v>79634</v>
+        <v>92193</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>483</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497431</v>
+        <v>497392</v>
       </c>
       <c r="R68" t="n">
-        <v>6832752</v>
+        <v>6832754</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7195,45 +7195,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129476431</v>
+        <v>129464850</v>
       </c>
       <c r="B69" t="n">
-        <v>92192</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497392</v>
+        <v>497345</v>
       </c>
       <c r="R69" t="n">
-        <v>6832754</v>
+        <v>6832696</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129465376</v>
+        <v>129476418</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497292</v>
+        <v>497415</v>
       </c>
       <c r="R6" t="n">
-        <v>6832709</v>
+        <v>6832767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1161,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476453</v>
+        <v>129465376</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497266</v>
+        <v>497292</v>
       </c>
       <c r="R7" t="n">
-        <v>6832713</v>
+        <v>6832709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476418</v>
+        <v>129476453</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497415</v>
+        <v>497266</v>
       </c>
       <c r="R8" t="n">
-        <v>6832767</v>
+        <v>6832713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476442</v>
+        <v>129467135</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497337</v>
+        <v>497389</v>
       </c>
       <c r="R10" t="n">
-        <v>6832676</v>
+        <v>6832791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129467135</v>
+        <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497389</v>
+        <v>497337</v>
       </c>
       <c r="R11" t="n">
-        <v>6832791</v>
+        <v>6832676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,12 +1646,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476426</v>
+        <v>129476428</v>
       </c>
       <c r="B14" t="n">
-        <v>97345</v>
+        <v>92836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497413</v>
+        <v>497387</v>
       </c>
       <c r="R14" t="n">
-        <v>6832724</v>
+        <v>6832781</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476423</v>
+        <v>129476426</v>
       </c>
       <c r="B15" t="n">
         <v>97345</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497256</v>
+        <v>497413</v>
       </c>
       <c r="R15" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,53 +2046,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476427</v>
+        <v>129476423</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>97345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497307</v>
+        <v>497256</v>
       </c>
       <c r="R16" t="n">
-        <v>6832769</v>
+        <v>6832740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,45 +2143,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476428</v>
+        <v>129476427</v>
       </c>
       <c r="B17" t="n">
-        <v>92836</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497387</v>
+        <v>497307</v>
       </c>
       <c r="R17" t="n">
-        <v>6832781</v>
+        <v>6832769</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129464182</v>
+        <v>129476437</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497410</v>
+        <v>497395</v>
       </c>
       <c r="R23" t="n">
-        <v>6832744</v>
+        <v>6832737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,22 +2818,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476437</v>
+        <v>129464182</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,34 +2841,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497395</v>
+        <v>497410</v>
       </c>
       <c r="R24" t="n">
-        <v>6832737</v>
+        <v>6832744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,12 +2915,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3024,45 +3024,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476446</v>
+        <v>129464639</v>
       </c>
       <c r="B26" t="n">
-        <v>91723</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497331</v>
+        <v>497352</v>
       </c>
       <c r="R26" t="n">
-        <v>6832758</v>
+        <v>6832732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,19 +3109,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129464639</v>
+        <v>129476454</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3152,14 +3152,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497352</v>
+        <v>497292</v>
       </c>
       <c r="R27" t="n">
-        <v>6832732</v>
+        <v>6832702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,44 +3206,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476454</v>
+        <v>129476446</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>91723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497292</v>
+        <v>497331</v>
       </c>
       <c r="R28" t="n">
-        <v>6832702</v>
+        <v>6832758</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476430</v>
+        <v>129476416</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>79663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497250</v>
+        <v>497395</v>
       </c>
       <c r="R29" t="n">
-        <v>6832730</v>
+        <v>6832737</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476450</v>
+        <v>129464293</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,37 +3423,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497272</v>
+        <v>497396</v>
       </c>
       <c r="R30" t="n">
-        <v>6832783</v>
+        <v>6832740</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3497,22 +3497,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129464293</v>
+        <v>129476450</v>
       </c>
       <c r="B31" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,37 +3520,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497396</v>
+        <v>497272</v>
       </c>
       <c r="R31" t="n">
-        <v>6832740</v>
+        <v>6832783</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3594,22 +3594,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476416</v>
+        <v>129476430</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497395</v>
+        <v>497250</v>
       </c>
       <c r="R32" t="n">
-        <v>6832737</v>
+        <v>6832730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476466</v>
+        <v>129476451</v>
       </c>
       <c r="B33" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497385</v>
+        <v>497241</v>
       </c>
       <c r="R33" t="n">
-        <v>6832779</v>
+        <v>6832763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476451</v>
+        <v>129476466</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497241</v>
+        <v>497385</v>
       </c>
       <c r="R34" t="n">
-        <v>6832763</v>
+        <v>6832779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R37" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B38" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R38" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476443</v>
+        <v>129465773</v>
       </c>
       <c r="B41" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497393</v>
+        <v>497256</v>
       </c>
       <c r="R41" t="n">
-        <v>6832735</v>
+        <v>6832783</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,12 +4564,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129465773</v>
+        <v>129476443</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4684,34 +4684,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497256</v>
+        <v>497393</v>
       </c>
       <c r="R43" t="n">
-        <v>6832783</v>
+        <v>6832735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4758,22 +4758,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476421</v>
+        <v>129465323</v>
       </c>
       <c r="B44" t="n">
-        <v>90582</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497336</v>
+        <v>497290</v>
       </c>
       <c r="R44" t="n">
-        <v>6832758</v>
+        <v>6832699</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,19 +4855,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476422</v>
+        <v>129476421</v>
       </c>
       <c r="B45" t="n">
         <v>90582</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497310</v>
+        <v>497336</v>
       </c>
       <c r="R45" t="n">
-        <v>6832692</v>
+        <v>6832758</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476424</v>
+        <v>129476422</v>
       </c>
       <c r="B46" t="n">
-        <v>97345</v>
+        <v>90582</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497389</v>
+        <v>497310</v>
       </c>
       <c r="R46" t="n">
-        <v>6832716</v>
+        <v>6832692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476433</v>
+        <v>129476424</v>
       </c>
       <c r="B47" t="n">
-        <v>91603</v>
+        <v>97345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>2569</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497349</v>
+        <v>497389</v>
       </c>
       <c r="R47" t="n">
-        <v>6832759</v>
+        <v>6832716</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129465323</v>
+        <v>129476433</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91603</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497290</v>
+        <v>497349</v>
       </c>
       <c r="R48" t="n">
-        <v>6832699</v>
+        <v>6832759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476460</v>
+        <v>129476456</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497427</v>
+        <v>497344</v>
       </c>
       <c r="R52" t="n">
-        <v>6832743</v>
+        <v>6832689</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476456</v>
+        <v>129476460</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497344</v>
+        <v>497427</v>
       </c>
       <c r="R53" t="n">
-        <v>6832689</v>
+        <v>6832743</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476434</v>
+        <v>129464078</v>
       </c>
       <c r="B55" t="n">
-        <v>91603</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,34 +5848,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497367</v>
+        <v>497426</v>
       </c>
       <c r="R55" t="n">
-        <v>6832720</v>
+        <v>6832743</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476439</v>
+        <v>129476434</v>
       </c>
       <c r="B56" t="n">
-        <v>78802</v>
+        <v>91603</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,21 +5945,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497415</v>
+        <v>497367</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6832720</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6031,7 +6031,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129464078</v>
+        <v>129466317</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497426</v>
+        <v>497335</v>
       </c>
       <c r="R57" t="n">
-        <v>6832743</v>
+        <v>6832765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129466317</v>
+        <v>129476439</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497335</v>
+        <v>497415</v>
       </c>
       <c r="R58" t="n">
-        <v>6832765</v>
+        <v>6832767</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6213,12 +6213,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476458</v>
+        <v>129476448</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497334</v>
+        <v>497361</v>
       </c>
       <c r="R60" t="n">
-        <v>6832718</v>
+        <v>6832760</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476448</v>
+        <v>129476458</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497361</v>
+        <v>497334</v>
       </c>
       <c r="R61" t="n">
-        <v>6832760</v>
+        <v>6832718</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476432</v>
+        <v>129466545</v>
       </c>
       <c r="B63" t="n">
-        <v>91603</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497389</v>
+        <v>497366</v>
       </c>
       <c r="R63" t="n">
-        <v>6832749</v>
+        <v>6832752</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,19 +6698,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129466545</v>
+        <v>129465171</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497366</v>
+        <v>497309</v>
       </c>
       <c r="R64" t="n">
-        <v>6832752</v>
+        <v>6832672</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129465171</v>
+        <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>91603</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497309</v>
+        <v>497389</v>
       </c>
       <c r="R65" t="n">
-        <v>6832672</v>
+        <v>6832749</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,57 +6892,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129465586</v>
+        <v>129476431</v>
       </c>
       <c r="B66" t="n">
-        <v>57887</v>
+        <v>92193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>483</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497254</v>
+        <v>497392</v>
       </c>
       <c r="R66" t="n">
-        <v>6832729</v>
+        <v>6832754</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,22 +6989,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129476420</v>
+        <v>129464850</v>
       </c>
       <c r="B67" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497431</v>
+        <v>497345</v>
       </c>
       <c r="R67" t="n">
-        <v>6832752</v>
+        <v>6832696</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,57 +7086,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476431</v>
+        <v>129465586</v>
       </c>
       <c r="B68" t="n">
-        <v>92193</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>483</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497392</v>
+        <v>497254</v>
       </c>
       <c r="R68" t="n">
-        <v>6832754</v>
+        <v>6832729</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129464850</v>
+        <v>129476420</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497345</v>
+        <v>497431</v>
       </c>
       <c r="R69" t="n">
-        <v>6832696</v>
+        <v>6832752</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129464751</v>
+        <v>129467135</v>
       </c>
       <c r="B9" t="n">
-        <v>90582</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497356</v>
+        <v>497389</v>
       </c>
       <c r="R9" t="n">
-        <v>6832723</v>
+        <v>6832791</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129467135</v>
+        <v>129476442</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497389</v>
+        <v>497337</v>
       </c>
       <c r="R10" t="n">
-        <v>6832791</v>
+        <v>6832676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>90582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,12 +1646,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476429</v>
+        <v>129464182</v>
       </c>
       <c r="B22" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497288</v>
+        <v>497410</v>
       </c>
       <c r="R22" t="n">
-        <v>6832771</v>
+        <v>6832744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476437</v>
+        <v>129476429</v>
       </c>
       <c r="B23" t="n">
-        <v>78802</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497395</v>
+        <v>497288</v>
       </c>
       <c r="R23" t="n">
-        <v>6832737</v>
+        <v>6832771</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129464182</v>
+        <v>129476437</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,34 +2841,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497410</v>
+        <v>497395</v>
       </c>
       <c r="R24" t="n">
-        <v>6832744</v>
+        <v>6832737</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,22 +2915,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476417</v>
+        <v>129464639</v>
       </c>
       <c r="B25" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,34 +2938,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497430</v>
+        <v>497352</v>
       </c>
       <c r="R25" t="n">
-        <v>6832760</v>
+        <v>6832732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,19 +3012,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129464639</v>
+        <v>129476454</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3055,14 +3055,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497352</v>
+        <v>497292</v>
       </c>
       <c r="R26" t="n">
-        <v>6832732</v>
+        <v>6832702</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,22 +3109,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476454</v>
+        <v>129476417</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497292</v>
+        <v>497430</v>
       </c>
       <c r="R27" t="n">
-        <v>6832702</v>
+        <v>6832760</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476416</v>
+        <v>129464293</v>
       </c>
       <c r="B29" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497395</v>
+        <v>497396</v>
       </c>
       <c r="R29" t="n">
-        <v>6832737</v>
+        <v>6832740</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129464293</v>
+        <v>129476416</v>
       </c>
       <c r="B30" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,37 +3423,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497396</v>
+        <v>497395</v>
       </c>
       <c r="R30" t="n">
-        <v>6832740</v>
+        <v>6832737</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3497,12 +3497,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476451</v>
+        <v>129476466</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497241</v>
+        <v>497385</v>
       </c>
       <c r="R33" t="n">
-        <v>6832763</v>
+        <v>6832779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476466</v>
+        <v>129476452</v>
       </c>
       <c r="B34" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497385</v>
+        <v>497258</v>
       </c>
       <c r="R34" t="n">
-        <v>6832779</v>
+        <v>6832721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476452</v>
+        <v>129476451</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497258</v>
+        <v>497241</v>
       </c>
       <c r="R35" t="n">
-        <v>6832721</v>
+        <v>6832763</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B37" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R37" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R38" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476455</v>
+        <v>129476436</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497307</v>
+        <v>497334</v>
       </c>
       <c r="R39" t="n">
-        <v>6832696</v>
+        <v>6832674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476436</v>
+        <v>129476455</v>
       </c>
       <c r="B40" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497334</v>
+        <v>497307</v>
       </c>
       <c r="R40" t="n">
-        <v>6832674</v>
+        <v>6832696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476439</v>
+        <v>129463331</v>
       </c>
       <c r="B58" t="n">
-        <v>78802</v>
+        <v>58162</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>102999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497415</v>
+        <v>497447</v>
       </c>
       <c r="R58" t="n">
         <v>6832767</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6213,22 +6213,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129463331</v>
+        <v>129476439</v>
       </c>
       <c r="B59" t="n">
-        <v>58162</v>
+        <v>78802</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,37 +6236,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102999</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497447</v>
+        <v>497415</v>
       </c>
       <c r="R59" t="n">
         <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,12 +6310,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129467135</v>
+        <v>129464751</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>90585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497389</v>
+        <v>497356</v>
       </c>
       <c r="R9" t="n">
-        <v>6832791</v>
+        <v>6832723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476442</v>
+        <v>129467135</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497337</v>
+        <v>497389</v>
       </c>
       <c r="R10" t="n">
-        <v>6832676</v>
+        <v>6832791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>90582</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R11" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,44 +1646,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476464</v>
+        <v>129476426</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>97348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497336</v>
+        <v>497413</v>
       </c>
       <c r="R12" t="n">
         <v>6832724</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476462</v>
+        <v>129476423</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>97348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497254</v>
+        <v>497256</v>
       </c>
       <c r="R13" t="n">
-        <v>6832752</v>
+        <v>6832740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,45 +1852,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476428</v>
+        <v>129465572</v>
       </c>
       <c r="B14" t="n">
-        <v>92836</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497387</v>
+        <v>497254</v>
       </c>
       <c r="R14" t="n">
-        <v>6832781</v>
+        <v>6832729</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1937,57 +1937,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476426</v>
+        <v>129476427</v>
       </c>
       <c r="B15" t="n">
-        <v>97345</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497413</v>
+        <v>497307</v>
       </c>
       <c r="R15" t="n">
-        <v>6832724</v>
+        <v>6832769</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,32 +2054,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476423</v>
+        <v>129476428</v>
       </c>
       <c r="B16" t="n">
-        <v>97345</v>
+        <v>92839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>4365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497256</v>
+        <v>497387</v>
       </c>
       <c r="R16" t="n">
-        <v>6832740</v>
+        <v>6832781</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476427</v>
+        <v>129476419</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,42 +2162,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497307</v>
+        <v>497336</v>
       </c>
       <c r="R17" t="n">
-        <v>6832769</v>
+        <v>6832679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129465572</v>
+        <v>129476464</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>78710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2259,34 +2259,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R18" t="n">
-        <v>6832729</v>
+        <v>6832724</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,22 +2333,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476419</v>
+        <v>129476462</v>
       </c>
       <c r="B19" t="n">
-        <v>79634</v>
+        <v>78710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497336</v>
+        <v>497254</v>
       </c>
       <c r="R19" t="n">
-        <v>6832679</v>
+        <v>6832752</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129464182</v>
+        <v>129476429</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497410</v>
+        <v>497288</v>
       </c>
       <c r="R22" t="n">
-        <v>6832744</v>
+        <v>6832771</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476429</v>
+        <v>129464182</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497288</v>
+        <v>497410</v>
       </c>
       <c r="R23" t="n">
-        <v>6832771</v>
+        <v>6832744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,12 +2818,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129464639</v>
+        <v>129476454</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -2958,14 +2958,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497352</v>
+        <v>497292</v>
       </c>
       <c r="R25" t="n">
-        <v>6832732</v>
+        <v>6832702</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,44 +3012,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476454</v>
+        <v>129476446</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497292</v>
+        <v>497331</v>
       </c>
       <c r="R26" t="n">
-        <v>6832702</v>
+        <v>6832758</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476417</v>
+        <v>129464639</v>
       </c>
       <c r="B27" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,34 +3132,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497430</v>
+        <v>497352</v>
       </c>
       <c r="R27" t="n">
-        <v>6832760</v>
+        <v>6832732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,44 +3206,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476446</v>
+        <v>129476417</v>
       </c>
       <c r="B28" t="n">
-        <v>91723</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497331</v>
+        <v>497430</v>
       </c>
       <c r="R28" t="n">
-        <v>6832758</v>
+        <v>6832760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476416</v>
+        <v>129476430</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497395</v>
+        <v>497250</v>
       </c>
       <c r="R30" t="n">
-        <v>6832737</v>
+        <v>6832730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476450</v>
+        <v>129476416</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497272</v>
+        <v>497395</v>
       </c>
       <c r="R31" t="n">
-        <v>6832783</v>
+        <v>6832737</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476430</v>
+        <v>129476450</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497250</v>
+        <v>497272</v>
       </c>
       <c r="R32" t="n">
-        <v>6832730</v>
+        <v>6832783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476466</v>
+        <v>129476452</v>
       </c>
       <c r="B33" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497385</v>
+        <v>497258</v>
       </c>
       <c r="R33" t="n">
-        <v>6832779</v>
+        <v>6832721</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476452</v>
+        <v>129476466</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497258</v>
+        <v>497385</v>
       </c>
       <c r="R34" t="n">
-        <v>6832721</v>
+        <v>6832779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476436</v>
+        <v>129476455</v>
       </c>
       <c r="B39" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497334</v>
+        <v>497307</v>
       </c>
       <c r="R39" t="n">
-        <v>6832674</v>
+        <v>6832696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476455</v>
+        <v>129476436</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497307</v>
+        <v>497334</v>
       </c>
       <c r="R40" t="n">
-        <v>6832696</v>
+        <v>6832674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129465323</v>
+        <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>90585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497290</v>
+        <v>497336</v>
       </c>
       <c r="R44" t="n">
-        <v>6832699</v>
+        <v>6832758</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,22 +4855,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476421</v>
+        <v>129476422</v>
       </c>
       <c r="B45" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497336</v>
+        <v>497310</v>
       </c>
       <c r="R45" t="n">
-        <v>6832758</v>
+        <v>6832692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476422</v>
+        <v>129476424</v>
       </c>
       <c r="B46" t="n">
-        <v>90582</v>
+        <v>97348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497310</v>
+        <v>497389</v>
       </c>
       <c r="R46" t="n">
-        <v>6832692</v>
+        <v>6832716</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476424</v>
+        <v>129476433</v>
       </c>
       <c r="B47" t="n">
-        <v>97345</v>
+        <v>91606</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2569</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497389</v>
+        <v>497349</v>
       </c>
       <c r="R47" t="n">
-        <v>6832716</v>
+        <v>6832759</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476433</v>
+        <v>129465323</v>
       </c>
       <c r="B48" t="n">
-        <v>91603</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497349</v>
+        <v>497290</v>
       </c>
       <c r="R48" t="n">
-        <v>6832759</v>
+        <v>6832699</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476456</v>
+        <v>129476460</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497344</v>
+        <v>497427</v>
       </c>
       <c r="R52" t="n">
-        <v>6832689</v>
+        <v>6832743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476460</v>
+        <v>129476456</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497427</v>
+        <v>497344</v>
       </c>
       <c r="R53" t="n">
-        <v>6832743</v>
+        <v>6832689</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476465</v>
+        <v>129464078</v>
       </c>
       <c r="B54" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497434</v>
+        <v>497426</v>
       </c>
       <c r="R54" t="n">
-        <v>6832759</v>
+        <v>6832743</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5825,19 +5825,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129464078</v>
+        <v>129466317</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497426</v>
+        <v>497335</v>
       </c>
       <c r="R55" t="n">
-        <v>6832743</v>
+        <v>6832765</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476434</v>
+        <v>129463331</v>
       </c>
       <c r="B56" t="n">
-        <v>91603</v>
+        <v>58162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,37 +5945,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>102999</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497367</v>
+        <v>497447</v>
       </c>
       <c r="R56" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6019,22 +6019,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129466317</v>
+        <v>129476439</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,34 +6042,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497335</v>
+        <v>497415</v>
       </c>
       <c r="R57" t="n">
-        <v>6832765</v>
+        <v>6832767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6116,22 +6116,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129463331</v>
+        <v>129476465</v>
       </c>
       <c r="B58" t="n">
-        <v>58162</v>
+        <v>78710</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102999</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497447</v>
+        <v>497434</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6213,22 +6213,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476439</v>
+        <v>129476434</v>
       </c>
       <c r="B59" t="n">
-        <v>78802</v>
+        <v>91606</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,21 +6236,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497415</v>
+        <v>497367</v>
       </c>
       <c r="R59" t="n">
-        <v>6832767</v>
+        <v>6832720</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476448</v>
+        <v>129476447</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497361</v>
+        <v>497367</v>
       </c>
       <c r="R60" t="n">
-        <v>6832760</v>
+        <v>6832744</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476447</v>
+        <v>129476448</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497367</v>
+        <v>497361</v>
       </c>
       <c r="R62" t="n">
-        <v>6832744</v>
+        <v>6832760</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>91603</v>
+        <v>91606</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>129476431</v>
       </c>
       <c r="B66" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464850</v>
+        <v>129465586</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497345</v>
+        <v>497254</v>
       </c>
       <c r="R67" t="n">
-        <v>6832696</v>
+        <v>6832729</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129465586</v>
+        <v>129476420</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>79634</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7109,34 +7109,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497254</v>
+        <v>497431</v>
       </c>
       <c r="R68" t="n">
-        <v>6832729</v>
+        <v>6832752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129476420</v>
+        <v>129464850</v>
       </c>
       <c r="B69" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497431</v>
+        <v>497345</v>
       </c>
       <c r="R69" t="n">
-        <v>6832752</v>
+        <v>6832696</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1658,32 +1658,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476426</v>
+        <v>129476462</v>
       </c>
       <c r="B12" t="n">
-        <v>97348</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497413</v>
+        <v>497254</v>
       </c>
       <c r="R12" t="n">
-        <v>6832724</v>
+        <v>6832752</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476423</v>
+        <v>129476428</v>
       </c>
       <c r="B13" t="n">
-        <v>97348</v>
+        <v>92839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497256</v>
+        <v>497387</v>
       </c>
       <c r="R13" t="n">
-        <v>6832740</v>
+        <v>6832781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129465572</v>
+        <v>129476464</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>78710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R14" t="n">
-        <v>6832729</v>
+        <v>6832724</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1937,65 +1937,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476427</v>
+        <v>129476426</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>97348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497307</v>
+        <v>497413</v>
       </c>
       <c r="R15" t="n">
-        <v>6832769</v>
+        <v>6832724</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476428</v>
+        <v>129476423</v>
       </c>
       <c r="B16" t="n">
-        <v>92839</v>
+        <v>97348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2089,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497387</v>
+        <v>497256</v>
       </c>
       <c r="R16" t="n">
-        <v>6832781</v>
+        <v>6832740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,10 +2143,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476419</v>
+        <v>129465572</v>
       </c>
       <c r="B17" t="n">
-        <v>79634</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,34 +2154,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497336</v>
+        <v>497254</v>
       </c>
       <c r="R17" t="n">
-        <v>6832679</v>
+        <v>6832729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,22 +2228,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476464</v>
+        <v>129476427</v>
       </c>
       <c r="B18" t="n">
-        <v>78710</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2259,34 +2251,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497336</v>
+        <v>497307</v>
       </c>
       <c r="R18" t="n">
-        <v>6832724</v>
+        <v>6832769</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476462</v>
+        <v>129476419</v>
       </c>
       <c r="B19" t="n">
-        <v>78710</v>
+        <v>79634</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R19" t="n">
-        <v>6832752</v>
+        <v>6832679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2927,32 +2927,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476454</v>
+        <v>129476446</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91726</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497292</v>
+        <v>497331</v>
       </c>
       <c r="R25" t="n">
-        <v>6832702</v>
+        <v>6832758</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3024,45 +3024,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476446</v>
+        <v>129464639</v>
       </c>
       <c r="B26" t="n">
-        <v>91726</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497331</v>
+        <v>497352</v>
       </c>
       <c r="R26" t="n">
-        <v>6832758</v>
+        <v>6832732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,19 +3109,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129464639</v>
+        <v>129476454</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3152,14 +3152,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497352</v>
+        <v>497292</v>
       </c>
       <c r="R27" t="n">
-        <v>6832732</v>
+        <v>6832702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,12 +3206,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476416</v>
+        <v>129476450</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497395</v>
+        <v>497272</v>
       </c>
       <c r="R31" t="n">
-        <v>6832737</v>
+        <v>6832783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476450</v>
+        <v>129476416</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497272</v>
+        <v>497395</v>
       </c>
       <c r="R32" t="n">
-        <v>6832783</v>
+        <v>6832737</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476452</v>
+        <v>129476466</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497258</v>
+        <v>497385</v>
       </c>
       <c r="R33" t="n">
-        <v>6832721</v>
+        <v>6832779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476466</v>
+        <v>129476451</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497385</v>
+        <v>497241</v>
       </c>
       <c r="R34" t="n">
-        <v>6832779</v>
+        <v>6832763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476451</v>
+        <v>129476452</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497241</v>
+        <v>497258</v>
       </c>
       <c r="R35" t="n">
-        <v>6832763</v>
+        <v>6832721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R37" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B38" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R38" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,7 +4479,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129465773</v>
+        <v>129464008</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497256</v>
+        <v>497425</v>
       </c>
       <c r="R41" t="n">
-        <v>6832783</v>
+        <v>6832750</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R42" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,22 +4661,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476443</v>
+        <v>129465773</v>
       </c>
       <c r="B43" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4684,34 +4684,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497393</v>
+        <v>497256</v>
       </c>
       <c r="R43" t="n">
-        <v>6832735</v>
+        <v>6832783</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4758,22 +4758,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476421</v>
+        <v>129465323</v>
       </c>
       <c r="B44" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497336</v>
+        <v>497290</v>
       </c>
       <c r="R44" t="n">
-        <v>6832758</v>
+        <v>6832699</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,19 +4855,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476422</v>
+        <v>129476421</v>
       </c>
       <c r="B45" t="n">
         <v>90585</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497310</v>
+        <v>497336</v>
       </c>
       <c r="R45" t="n">
-        <v>6832692</v>
+        <v>6832758</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476424</v>
+        <v>129476422</v>
       </c>
       <c r="B46" t="n">
-        <v>97348</v>
+        <v>90585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497389</v>
+        <v>497310</v>
       </c>
       <c r="R46" t="n">
-        <v>6832716</v>
+        <v>6832692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476433</v>
+        <v>129476424</v>
       </c>
       <c r="B47" t="n">
-        <v>91606</v>
+        <v>97348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>2569</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497349</v>
+        <v>497389</v>
       </c>
       <c r="R47" t="n">
-        <v>6832759</v>
+        <v>6832716</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129465323</v>
+        <v>129476433</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497290</v>
+        <v>497349</v>
       </c>
       <c r="R48" t="n">
-        <v>6832699</v>
+        <v>6832759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476460</v>
+        <v>129476456</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497427</v>
+        <v>497344</v>
       </c>
       <c r="R52" t="n">
-        <v>6832743</v>
+        <v>6832689</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476456</v>
+        <v>129476460</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497344</v>
+        <v>497427</v>
       </c>
       <c r="R53" t="n">
-        <v>6832689</v>
+        <v>6832743</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129464078</v>
+        <v>129476434</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497426</v>
+        <v>497367</v>
       </c>
       <c r="R54" t="n">
-        <v>6832743</v>
+        <v>6832720</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5825,19 +5825,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129466317</v>
+        <v>129464078</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497335</v>
+        <v>497426</v>
       </c>
       <c r="R55" t="n">
-        <v>6832765</v>
+        <v>6832743</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129463331</v>
+        <v>129466317</v>
       </c>
       <c r="B56" t="n">
-        <v>58162</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,21 +5945,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102999</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5969,13 +5969,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497447</v>
+        <v>497335</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6832765</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476439</v>
+        <v>129463331</v>
       </c>
       <c r="B57" t="n">
-        <v>78802</v>
+        <v>58162</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,37 +6042,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>102999</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497415</v>
+        <v>497447</v>
       </c>
       <c r="R57" t="n">
         <v>6832767</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6116,12 +6116,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6225,10 +6225,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476434</v>
+        <v>129476439</v>
       </c>
       <c r="B59" t="n">
-        <v>91606</v>
+        <v>78802</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,21 +6236,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497367</v>
+        <v>497415</v>
       </c>
       <c r="R59" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476447</v>
+        <v>129476458</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497367</v>
+        <v>497334</v>
       </c>
       <c r="R60" t="n">
-        <v>6832744</v>
+        <v>6832718</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476458</v>
+        <v>129476448</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497334</v>
+        <v>497361</v>
       </c>
       <c r="R61" t="n">
-        <v>6832718</v>
+        <v>6832760</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476448</v>
+        <v>129476447</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497361</v>
+        <v>497367</v>
       </c>
       <c r="R62" t="n">
-        <v>6832760</v>
+        <v>6832744</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129465586</v>
+        <v>129464850</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497254</v>
+        <v>497345</v>
       </c>
       <c r="R67" t="n">
-        <v>6832729</v>
+        <v>6832696</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476420</v>
+        <v>129465586</v>
       </c>
       <c r="B68" t="n">
-        <v>79634</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7109,34 +7109,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497431</v>
+        <v>497254</v>
       </c>
       <c r="R68" t="n">
-        <v>6832752</v>
+        <v>6832729</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129464850</v>
+        <v>129476420</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497345</v>
+        <v>497431</v>
       </c>
       <c r="R69" t="n">
-        <v>6832696</v>
+        <v>6832752</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1658,7 +1658,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476462</v>
+        <v>129476464</v>
       </c>
       <c r="B12" t="n">
         <v>78710</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R12" t="n">
-        <v>6832752</v>
+        <v>6832724</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476428</v>
+        <v>129476462</v>
       </c>
       <c r="B13" t="n">
-        <v>92839</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497387</v>
+        <v>497254</v>
       </c>
       <c r="R13" t="n">
-        <v>6832781</v>
+        <v>6832752</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476464</v>
+        <v>129465572</v>
       </c>
       <c r="B14" t="n">
-        <v>78710</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497336</v>
+        <v>497254</v>
       </c>
       <c r="R14" t="n">
-        <v>6832724</v>
+        <v>6832729</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1937,57 +1937,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476426</v>
+        <v>129476427</v>
       </c>
       <c r="B15" t="n">
-        <v>97348</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497413</v>
+        <v>497307</v>
       </c>
       <c r="R15" t="n">
-        <v>6832724</v>
+        <v>6832769</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,7 +2054,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476423</v>
+        <v>129476426</v>
       </c>
       <c r="B16" t="n">
         <v>97348</v>
@@ -2081,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497256</v>
+        <v>497413</v>
       </c>
       <c r="R16" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,45 +2151,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129465572</v>
+        <v>129476423</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>97348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497254</v>
+        <v>497256</v>
       </c>
       <c r="R17" t="n">
-        <v>6832729</v>
+        <v>6832740</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2228,65 +2236,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476427</v>
+        <v>129476428</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>92839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497307</v>
+        <v>497387</v>
       </c>
       <c r="R18" t="n">
-        <v>6832769</v>
+        <v>6832781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476429</v>
+        <v>129476437</v>
       </c>
       <c r="B22" t="n">
-        <v>80150</v>
+        <v>78802</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497288</v>
+        <v>497395</v>
       </c>
       <c r="R22" t="n">
-        <v>6832771</v>
+        <v>6832737</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476437</v>
+        <v>129476429</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497395</v>
+        <v>497288</v>
       </c>
       <c r="R24" t="n">
-        <v>6832737</v>
+        <v>6832771</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476454</v>
+        <v>129476417</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497292</v>
+        <v>497430</v>
       </c>
       <c r="R27" t="n">
-        <v>6832702</v>
+        <v>6832760</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476417</v>
+        <v>129476454</v>
       </c>
       <c r="B28" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497430</v>
+        <v>497292</v>
       </c>
       <c r="R28" t="n">
-        <v>6832760</v>
+        <v>6832702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B37" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R37" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R38" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R41" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,22 +4564,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476443</v>
+        <v>129464008</v>
       </c>
       <c r="B42" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497393</v>
+        <v>497425</v>
       </c>
       <c r="R42" t="n">
-        <v>6832735</v>
+        <v>6832750</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,12 +4661,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129465323</v>
+        <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>90585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497290</v>
+        <v>497336</v>
       </c>
       <c r="R44" t="n">
-        <v>6832699</v>
+        <v>6832758</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,19 +4855,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476421</v>
+        <v>129476422</v>
       </c>
       <c r="B45" t="n">
         <v>90585</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497336</v>
+        <v>497310</v>
       </c>
       <c r="R45" t="n">
-        <v>6832758</v>
+        <v>6832692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476422</v>
+        <v>129476424</v>
       </c>
       <c r="B46" t="n">
-        <v>90585</v>
+        <v>97348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497310</v>
+        <v>497389</v>
       </c>
       <c r="R46" t="n">
-        <v>6832692</v>
+        <v>6832716</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476424</v>
+        <v>129476433</v>
       </c>
       <c r="B47" t="n">
-        <v>97348</v>
+        <v>91606</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2569</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497389</v>
+        <v>497349</v>
       </c>
       <c r="R47" t="n">
-        <v>6832716</v>
+        <v>6832759</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476433</v>
+        <v>129465323</v>
       </c>
       <c r="B48" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497349</v>
+        <v>497290</v>
       </c>
       <c r="R48" t="n">
-        <v>6832759</v>
+        <v>6832699</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B50" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R50" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476463</v>
+        <v>129476461</v>
       </c>
       <c r="B51" t="n">
         <v>78710</v>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497356</v>
+        <v>497297</v>
       </c>
       <c r="R51" t="n">
-        <v>6832686</v>
+        <v>6832767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R52" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476460</v>
+        <v>129476456</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497427</v>
+        <v>497344</v>
       </c>
       <c r="R53" t="n">
-        <v>6832743</v>
+        <v>6832689</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129463331</v>
+        <v>129476465</v>
       </c>
       <c r="B57" t="n">
-        <v>58162</v>
+        <v>78710</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,37 +6042,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102999</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497447</v>
+        <v>497434</v>
       </c>
       <c r="R57" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6116,22 +6116,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476465</v>
+        <v>129463331</v>
       </c>
       <c r="B58" t="n">
-        <v>78710</v>
+        <v>58162</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>102999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497434</v>
+        <v>497447</v>
       </c>
       <c r="R58" t="n">
-        <v>6832759</v>
+        <v>6832767</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6213,12 +6213,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476458</v>
+        <v>129476448</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497334</v>
+        <v>497361</v>
       </c>
       <c r="R60" t="n">
-        <v>6832718</v>
+        <v>6832760</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476448</v>
+        <v>129476458</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497361</v>
+        <v>497334</v>
       </c>
       <c r="R61" t="n">
-        <v>6832760</v>
+        <v>6832718</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129466545</v>
+        <v>129476432</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497366</v>
+        <v>497389</v>
       </c>
       <c r="R63" t="n">
-        <v>6832752</v>
+        <v>6832749</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,19 +6698,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129465171</v>
+        <v>129466545</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497309</v>
+        <v>497366</v>
       </c>
       <c r="R64" t="n">
-        <v>6832672</v>
+        <v>6832752</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129476432</v>
+        <v>129465171</v>
       </c>
       <c r="B65" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497389</v>
+        <v>497309</v>
       </c>
       <c r="R65" t="n">
-        <v>6832749</v>
+        <v>6832672</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,12 +6892,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129476418</v>
+        <v>129465376</v>
       </c>
       <c r="B6" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497415</v>
+        <v>497292</v>
       </c>
       <c r="R6" t="n">
-        <v>6832767</v>
+        <v>6832709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1161,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R7" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476453</v>
+        <v>129476418</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497266</v>
+        <v>497415</v>
       </c>
       <c r="R8" t="n">
-        <v>6832713</v>
+        <v>6832767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129464751</v>
+        <v>129467135</v>
       </c>
       <c r="B9" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497356</v>
+        <v>497389</v>
       </c>
       <c r="R9" t="n">
-        <v>6832723</v>
+        <v>6832791</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129467135</v>
+        <v>129464751</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>90585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497389</v>
+        <v>497356</v>
       </c>
       <c r="R10" t="n">
-        <v>6832791</v>
+        <v>6832723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,32 +1658,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476464</v>
+        <v>129476428</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>92839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497336</v>
+        <v>497387</v>
       </c>
       <c r="R12" t="n">
-        <v>6832724</v>
+        <v>6832781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476462</v>
+        <v>129476427</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,34 +1766,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497254</v>
+        <v>497307</v>
       </c>
       <c r="R13" t="n">
-        <v>6832752</v>
+        <v>6832769</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476427</v>
+        <v>129476462</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>78710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,42 +1968,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497307</v>
+        <v>497254</v>
       </c>
       <c r="R15" t="n">
-        <v>6832769</v>
+        <v>6832752</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,32 +2054,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476426</v>
+        <v>129476464</v>
       </c>
       <c r="B16" t="n">
-        <v>97348</v>
+        <v>78710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497413</v>
+        <v>497336</v>
       </c>
       <c r="R16" t="n">
         <v>6832724</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476423</v>
+        <v>129476426</v>
       </c>
       <c r="B17" t="n">
         <v>97348</v>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497256</v>
+        <v>497413</v>
       </c>
       <c r="R17" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476428</v>
+        <v>129476423</v>
       </c>
       <c r="B18" t="n">
-        <v>92839</v>
+        <v>97348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497387</v>
+        <v>497256</v>
       </c>
       <c r="R18" t="n">
-        <v>6832781</v>
+        <v>6832740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476437</v>
+        <v>129464182</v>
       </c>
       <c r="B22" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497395</v>
+        <v>497410</v>
       </c>
       <c r="R22" t="n">
-        <v>6832737</v>
+        <v>6832744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129464182</v>
+        <v>129476429</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497410</v>
+        <v>497288</v>
       </c>
       <c r="R23" t="n">
-        <v>6832744</v>
+        <v>6832771</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,22 +2818,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476429</v>
+        <v>129476437</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>78802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497288</v>
+        <v>497395</v>
       </c>
       <c r="R24" t="n">
-        <v>6832771</v>
+        <v>6832737</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2927,45 +2927,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476446</v>
+        <v>129464639</v>
       </c>
       <c r="B25" t="n">
-        <v>91726</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497331</v>
+        <v>497352</v>
       </c>
       <c r="R25" t="n">
-        <v>6832758</v>
+        <v>6832732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,19 +3012,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129464639</v>
+        <v>129476454</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3055,14 +3055,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497352</v>
+        <v>497292</v>
       </c>
       <c r="R26" t="n">
-        <v>6832732</v>
+        <v>6832702</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,12 +3109,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476454</v>
+        <v>129476446</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>91726</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497292</v>
+        <v>497331</v>
       </c>
       <c r="R28" t="n">
-        <v>6832702</v>
+        <v>6832758</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129464293</v>
+        <v>129476450</v>
       </c>
       <c r="B29" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497396</v>
+        <v>497272</v>
       </c>
       <c r="R29" t="n">
-        <v>6832740</v>
+        <v>6832783</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476430</v>
+        <v>129476416</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497250</v>
+        <v>497395</v>
       </c>
       <c r="R30" t="n">
-        <v>6832730</v>
+        <v>6832737</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476450</v>
+        <v>129476430</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497272</v>
+        <v>497250</v>
       </c>
       <c r="R31" t="n">
-        <v>6832783</v>
+        <v>6832730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476416</v>
+        <v>129464293</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,37 +3617,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497395</v>
+        <v>497396</v>
       </c>
       <c r="R32" t="n">
-        <v>6832737</v>
+        <v>6832740</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3691,44 +3691,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476466</v>
+        <v>129476435</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497385</v>
+        <v>497301</v>
       </c>
       <c r="R33" t="n">
-        <v>6832779</v>
+        <v>6832764</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476451</v>
+        <v>129476466</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497241</v>
+        <v>497385</v>
       </c>
       <c r="R34" t="n">
-        <v>6832763</v>
+        <v>6832779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476452</v>
+        <v>129476451</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497258</v>
+        <v>497241</v>
       </c>
       <c r="R35" t="n">
-        <v>6832721</v>
+        <v>6832763</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476435</v>
+        <v>129476452</v>
       </c>
       <c r="B36" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497301</v>
+        <v>497258</v>
       </c>
       <c r="R36" t="n">
-        <v>6832764</v>
+        <v>6832721</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476443</v>
+        <v>129464008</v>
       </c>
       <c r="B41" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497393</v>
+        <v>497425</v>
       </c>
       <c r="R41" t="n">
-        <v>6832735</v>
+        <v>6832750</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,22 +4564,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R42" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,12 +4661,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476421</v>
+        <v>129465323</v>
       </c>
       <c r="B44" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497336</v>
+        <v>497290</v>
       </c>
       <c r="R44" t="n">
-        <v>6832758</v>
+        <v>6832699</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,19 +4855,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476422</v>
+        <v>129476421</v>
       </c>
       <c r="B45" t="n">
         <v>90585</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497310</v>
+        <v>497336</v>
       </c>
       <c r="R45" t="n">
-        <v>6832692</v>
+        <v>6832758</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476424</v>
+        <v>129476422</v>
       </c>
       <c r="B46" t="n">
-        <v>97348</v>
+        <v>90585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497389</v>
+        <v>497310</v>
       </c>
       <c r="R46" t="n">
-        <v>6832716</v>
+        <v>6832692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476433</v>
+        <v>129476424</v>
       </c>
       <c r="B47" t="n">
-        <v>91606</v>
+        <v>97348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>2569</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497349</v>
+        <v>497389</v>
       </c>
       <c r="R47" t="n">
-        <v>6832759</v>
+        <v>6832716</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129465323</v>
+        <v>129476433</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497290</v>
+        <v>497349</v>
       </c>
       <c r="R48" t="n">
-        <v>6832699</v>
+        <v>6832759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476461</v>
+        <v>129476456</v>
       </c>
       <c r="B51" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497297</v>
+        <v>497344</v>
       </c>
       <c r="R51" t="n">
-        <v>6832767</v>
+        <v>6832689</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476463</v>
+        <v>129476461</v>
       </c>
       <c r="B52" t="n">
         <v>78710</v>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497356</v>
+        <v>497297</v>
       </c>
       <c r="R52" t="n">
-        <v>6832686</v>
+        <v>6832767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R53" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476434</v>
+        <v>129464078</v>
       </c>
       <c r="B54" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497367</v>
+        <v>497426</v>
       </c>
       <c r="R54" t="n">
-        <v>6832720</v>
+        <v>6832743</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5825,19 +5825,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129464078</v>
+        <v>129466317</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497426</v>
+        <v>497335</v>
       </c>
       <c r="R55" t="n">
-        <v>6832743</v>
+        <v>6832765</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129466317</v>
+        <v>129463331</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>58162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,21 +5945,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>102999</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5969,13 +5969,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497335</v>
+        <v>497447</v>
       </c>
       <c r="R56" t="n">
-        <v>6832765</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476465</v>
+        <v>129476434</v>
       </c>
       <c r="B57" t="n">
-        <v>78710</v>
+        <v>91606</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,21 +6042,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497434</v>
+        <v>497367</v>
       </c>
       <c r="R57" t="n">
-        <v>6832759</v>
+        <v>6832720</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129463331</v>
+        <v>129476465</v>
       </c>
       <c r="B58" t="n">
-        <v>58162</v>
+        <v>78710</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102999</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497447</v>
+        <v>497434</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6213,12 +6213,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476432</v>
+        <v>129466545</v>
       </c>
       <c r="B63" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497389</v>
+        <v>497366</v>
       </c>
       <c r="R63" t="n">
-        <v>6832749</v>
+        <v>6832752</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,19 +6698,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129466545</v>
+        <v>129465171</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497366</v>
+        <v>497309</v>
       </c>
       <c r="R64" t="n">
-        <v>6832752</v>
+        <v>6832672</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129465171</v>
+        <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497309</v>
+        <v>497389</v>
       </c>
       <c r="R65" t="n">
-        <v>6832672</v>
+        <v>6832749</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,57 +6892,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129476431</v>
+        <v>129465586</v>
       </c>
       <c r="B66" t="n">
-        <v>92196</v>
+        <v>57887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>483</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497392</v>
+        <v>497254</v>
       </c>
       <c r="R66" t="n">
-        <v>6832754</v>
+        <v>6832729</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,12 +6989,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7098,45 +7098,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129465586</v>
+        <v>129476431</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>92196</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>483</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497254</v>
+        <v>497392</v>
       </c>
       <c r="R68" t="n">
-        <v>6832729</v>
+        <v>6832754</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,12 +7183,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,7 +1076,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1107,14 +1107,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R6" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,22 +1161,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476453</v>
+        <v>129476418</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497266</v>
+        <v>497415</v>
       </c>
       <c r="R7" t="n">
-        <v>6832713</v>
+        <v>6832767</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476418</v>
+        <v>129465376</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497415</v>
+        <v>497292</v>
       </c>
       <c r="R8" t="n">
-        <v>6832767</v>
+        <v>6832709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,22 +1355,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129467135</v>
+        <v>129464751</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>90585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497389</v>
+        <v>497356</v>
       </c>
       <c r="R9" t="n">
-        <v>6832791</v>
+        <v>6832723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B10" t="n">
-        <v>90585</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R10" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129467135</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497389</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832791</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,44 +1646,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476428</v>
+        <v>129476464</v>
       </c>
       <c r="B12" t="n">
-        <v>92839</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497387</v>
+        <v>497336</v>
       </c>
       <c r="R12" t="n">
-        <v>6832781</v>
+        <v>6832724</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476427</v>
+        <v>129476462</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,42 +1766,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497307</v>
+        <v>497254</v>
       </c>
       <c r="R13" t="n">
-        <v>6832769</v>
+        <v>6832752</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1860,45 +1852,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129465572</v>
+        <v>129476426</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>97348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497254</v>
+        <v>497413</v>
       </c>
       <c r="R14" t="n">
-        <v>6832729</v>
+        <v>6832724</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,44 +1937,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476462</v>
+        <v>129476423</v>
       </c>
       <c r="B15" t="n">
-        <v>78710</v>
+        <v>97348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497254</v>
+        <v>497256</v>
       </c>
       <c r="R15" t="n">
-        <v>6832752</v>
+        <v>6832740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476464</v>
+        <v>129476428</v>
       </c>
       <c r="B16" t="n">
-        <v>78710</v>
+        <v>92839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2089,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497336</v>
+        <v>497387</v>
       </c>
       <c r="R16" t="n">
-        <v>6832724</v>
+        <v>6832781</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,45 +2143,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476426</v>
+        <v>129465572</v>
       </c>
       <c r="B17" t="n">
-        <v>97348</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497413</v>
+        <v>497254</v>
       </c>
       <c r="R17" t="n">
-        <v>6832724</v>
+        <v>6832729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,57 +2228,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476423</v>
+        <v>129476427</v>
       </c>
       <c r="B18" t="n">
-        <v>97348</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497256</v>
+        <v>497307</v>
       </c>
       <c r="R18" t="n">
-        <v>6832740</v>
+        <v>6832769</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476449</v>
+        <v>129476457</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497318</v>
+        <v>497355</v>
       </c>
       <c r="R20" t="n">
-        <v>6832776</v>
+        <v>6832689</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476457</v>
+        <v>129476449</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497355</v>
+        <v>497318</v>
       </c>
       <c r="R21" t="n">
-        <v>6832689</v>
+        <v>6832776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,45 +2927,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129464639</v>
+        <v>129476446</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91726</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497352</v>
+        <v>497331</v>
       </c>
       <c r="R25" t="n">
-        <v>6832732</v>
+        <v>6832758</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,22 +3012,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476454</v>
+        <v>129476417</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497292</v>
+        <v>497430</v>
       </c>
       <c r="R26" t="n">
-        <v>6832702</v>
+        <v>6832760</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476417</v>
+        <v>129464639</v>
       </c>
       <c r="B27" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,34 +3132,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497430</v>
+        <v>497352</v>
       </c>
       <c r="R27" t="n">
-        <v>6832760</v>
+        <v>6832732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,44 +3206,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476446</v>
+        <v>129476454</v>
       </c>
       <c r="B28" t="n">
-        <v>91726</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497331</v>
+        <v>497292</v>
       </c>
       <c r="R28" t="n">
-        <v>6832758</v>
+        <v>6832702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476450</v>
+        <v>129464293</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497272</v>
+        <v>497396</v>
       </c>
       <c r="R29" t="n">
-        <v>6832783</v>
+        <v>6832740</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476416</v>
+        <v>129476430</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497395</v>
+        <v>497250</v>
       </c>
       <c r="R30" t="n">
-        <v>6832737</v>
+        <v>6832730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476430</v>
+        <v>129476450</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497250</v>
+        <v>497272</v>
       </c>
       <c r="R31" t="n">
-        <v>6832730</v>
+        <v>6832783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129464293</v>
+        <v>129476416</v>
       </c>
       <c r="B32" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,37 +3617,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497396</v>
+        <v>497395</v>
       </c>
       <c r="R32" t="n">
-        <v>6832740</v>
+        <v>6832737</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3691,44 +3691,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476435</v>
+        <v>129476466</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497301</v>
+        <v>497385</v>
       </c>
       <c r="R33" t="n">
-        <v>6832764</v>
+        <v>6832779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476466</v>
+        <v>129476451</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497385</v>
+        <v>497241</v>
       </c>
       <c r="R34" t="n">
-        <v>6832779</v>
+        <v>6832763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476451</v>
+        <v>129476452</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497241</v>
+        <v>497258</v>
       </c>
       <c r="R35" t="n">
-        <v>6832763</v>
+        <v>6832721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476452</v>
+        <v>129476435</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497258</v>
+        <v>497301</v>
       </c>
       <c r="R36" t="n">
-        <v>6832721</v>
+        <v>6832764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476455</v>
+        <v>129476436</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497307</v>
+        <v>497334</v>
       </c>
       <c r="R39" t="n">
-        <v>6832696</v>
+        <v>6832674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476436</v>
+        <v>129476455</v>
       </c>
       <c r="B40" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497334</v>
+        <v>497307</v>
       </c>
       <c r="R40" t="n">
-        <v>6832674</v>
+        <v>6832696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129465323</v>
+        <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>90585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497290</v>
+        <v>497336</v>
       </c>
       <c r="R44" t="n">
-        <v>6832699</v>
+        <v>6832758</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,19 +4855,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476421</v>
+        <v>129476422</v>
       </c>
       <c r="B45" t="n">
         <v>90585</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497336</v>
+        <v>497310</v>
       </c>
       <c r="R45" t="n">
-        <v>6832758</v>
+        <v>6832692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476422</v>
+        <v>129476424</v>
       </c>
       <c r="B46" t="n">
-        <v>90585</v>
+        <v>97348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497310</v>
+        <v>497389</v>
       </c>
       <c r="R46" t="n">
-        <v>6832692</v>
+        <v>6832716</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476424</v>
+        <v>129476433</v>
       </c>
       <c r="B47" t="n">
-        <v>97348</v>
+        <v>91606</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2569</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497389</v>
+        <v>497349</v>
       </c>
       <c r="R47" t="n">
-        <v>6832716</v>
+        <v>6832759</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476433</v>
+        <v>129465323</v>
       </c>
       <c r="B48" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497349</v>
+        <v>497290</v>
       </c>
       <c r="R48" t="n">
-        <v>6832759</v>
+        <v>6832699</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476460</v>
+        <v>129476461</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497427</v>
+        <v>497297</v>
       </c>
       <c r="R50" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R51" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R52" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R53" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129464078</v>
+        <v>129476434</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497426</v>
+        <v>497367</v>
       </c>
       <c r="R54" t="n">
-        <v>6832743</v>
+        <v>6832720</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5825,22 +5825,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129466317</v>
+        <v>129476465</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,34 +5848,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497335</v>
+        <v>497434</v>
       </c>
       <c r="R55" t="n">
-        <v>6832765</v>
+        <v>6832759</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129463331</v>
+        <v>129466317</v>
       </c>
       <c r="B56" t="n">
-        <v>58162</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,21 +5945,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102999</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5969,13 +5969,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497447</v>
+        <v>497335</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6832765</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476434</v>
+        <v>129476439</v>
       </c>
       <c r="B57" t="n">
-        <v>91606</v>
+        <v>78802</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,21 +6042,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497367</v>
+        <v>497415</v>
       </c>
       <c r="R57" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476465</v>
+        <v>129464078</v>
       </c>
       <c r="B58" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497434</v>
+        <v>497426</v>
       </c>
       <c r="R58" t="n">
-        <v>6832759</v>
+        <v>6832743</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6213,22 +6213,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476439</v>
+        <v>129463331</v>
       </c>
       <c r="B59" t="n">
-        <v>78802</v>
+        <v>58162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,37 +6236,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>102999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497415</v>
+        <v>497447</v>
       </c>
       <c r="R59" t="n">
         <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,12 +6310,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129466545</v>
+        <v>129476432</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497366</v>
+        <v>497389</v>
       </c>
       <c r="R63" t="n">
-        <v>6832752</v>
+        <v>6832749</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,12 +6698,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129476432</v>
+        <v>129466545</v>
       </c>
       <c r="B65" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497389</v>
+        <v>497366</v>
       </c>
       <c r="R65" t="n">
-        <v>6832749</v>
+        <v>6832752</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,22 +6892,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129465586</v>
+        <v>129464850</v>
       </c>
       <c r="B66" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6915,21 +6915,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497254</v>
+        <v>497345</v>
       </c>
       <c r="R66" t="n">
-        <v>6832729</v>
+        <v>6832696</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464850</v>
+        <v>129465586</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497345</v>
+        <v>497254</v>
       </c>
       <c r="R67" t="n">
-        <v>6832696</v>
+        <v>6832729</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129476453</v>
+        <v>129476418</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497266</v>
+        <v>497415</v>
       </c>
       <c r="R6" t="n">
-        <v>6832713</v>
+        <v>6832767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476418</v>
+        <v>129465376</v>
       </c>
       <c r="B7" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,34 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497415</v>
+        <v>497292</v>
       </c>
       <c r="R7" t="n">
-        <v>6832767</v>
+        <v>6832709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1258,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1301,14 +1301,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R8" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,22 +1355,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129464751</v>
+        <v>129467135</v>
       </c>
       <c r="B9" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497356</v>
+        <v>497389</v>
       </c>
       <c r="R9" t="n">
-        <v>6832723</v>
+        <v>6832791</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>90585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R10" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129467135</v>
+        <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497389</v>
+        <v>497337</v>
       </c>
       <c r="R11" t="n">
-        <v>6832791</v>
+        <v>6832676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,22 +1646,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476464</v>
+        <v>129476427</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,34 +1669,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497336</v>
+        <v>497307</v>
       </c>
       <c r="R12" t="n">
-        <v>6832724</v>
+        <v>6832769</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,10 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476462</v>
+        <v>129465572</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,34 +1774,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>497254</v>
       </c>
       <c r="R13" t="n">
-        <v>6832752</v>
+        <v>6832729</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,44 +1848,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476426</v>
+        <v>129476464</v>
       </c>
       <c r="B14" t="n">
-        <v>97348</v>
+        <v>78710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,7 +1895,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497413</v>
+        <v>497336</v>
       </c>
       <c r="R14" t="n">
         <v>6832724</v>
@@ -1949,7 +1957,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476423</v>
+        <v>129476426</v>
       </c>
       <c r="B15" t="n">
         <v>97348</v>
@@ -1984,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497256</v>
+        <v>497413</v>
       </c>
       <c r="R15" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,32 +2054,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476428</v>
+        <v>129476462</v>
       </c>
       <c r="B16" t="n">
-        <v>92839</v>
+        <v>78710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497387</v>
+        <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832781</v>
+        <v>6832752</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,45 +2151,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129465572</v>
+        <v>129476423</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>97348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497254</v>
+        <v>497256</v>
       </c>
       <c r="R17" t="n">
-        <v>6832729</v>
+        <v>6832740</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2228,65 +2236,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476427</v>
+        <v>129476428</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>92839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497307</v>
+        <v>497387</v>
       </c>
       <c r="R18" t="n">
-        <v>6832769</v>
+        <v>6832781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476457</v>
+        <v>129476449</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497355</v>
+        <v>497318</v>
       </c>
       <c r="R20" t="n">
-        <v>6832689</v>
+        <v>6832776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476449</v>
+        <v>129476457</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497318</v>
+        <v>497355</v>
       </c>
       <c r="R21" t="n">
-        <v>6832776</v>
+        <v>6832689</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,45 +2927,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476446</v>
+        <v>129464639</v>
       </c>
       <c r="B25" t="n">
-        <v>91726</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497331</v>
+        <v>497352</v>
       </c>
       <c r="R25" t="n">
-        <v>6832758</v>
+        <v>6832732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,12 +3012,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129464639</v>
+        <v>129476454</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3152,14 +3152,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497352</v>
+        <v>497292</v>
       </c>
       <c r="R27" t="n">
-        <v>6832732</v>
+        <v>6832702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,44 +3206,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476454</v>
+        <v>129476446</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>91726</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497292</v>
+        <v>497331</v>
       </c>
       <c r="R28" t="n">
-        <v>6832702</v>
+        <v>6832758</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129464293</v>
+        <v>129476450</v>
       </c>
       <c r="B29" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497396</v>
+        <v>497272</v>
       </c>
       <c r="R29" t="n">
-        <v>6832740</v>
+        <v>6832783</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476430</v>
+        <v>129476416</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497250</v>
+        <v>497395</v>
       </c>
       <c r="R30" t="n">
-        <v>6832730</v>
+        <v>6832737</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476450</v>
+        <v>129464293</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,37 +3520,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497272</v>
+        <v>497396</v>
       </c>
       <c r="R31" t="n">
-        <v>6832783</v>
+        <v>6832740</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3594,22 +3594,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476416</v>
+        <v>129476430</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497395</v>
+        <v>497250</v>
       </c>
       <c r="R32" t="n">
-        <v>6832737</v>
+        <v>6832730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476451</v>
+        <v>129476435</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497241</v>
+        <v>497301</v>
       </c>
       <c r="R34" t="n">
-        <v>6832763</v>
+        <v>6832764</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476452</v>
+        <v>129476451</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497258</v>
+        <v>497241</v>
       </c>
       <c r="R35" t="n">
-        <v>6832721</v>
+        <v>6832763</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476435</v>
+        <v>129476452</v>
       </c>
       <c r="B36" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497301</v>
+        <v>497258</v>
       </c>
       <c r="R36" t="n">
-        <v>6832764</v>
+        <v>6832721</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476421</v>
+        <v>129465323</v>
       </c>
       <c r="B44" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497336</v>
+        <v>497290</v>
       </c>
       <c r="R44" t="n">
-        <v>6832758</v>
+        <v>6832699</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,19 +4855,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476422</v>
+        <v>129476421</v>
       </c>
       <c r="B45" t="n">
         <v>90585</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497310</v>
+        <v>497336</v>
       </c>
       <c r="R45" t="n">
-        <v>6832692</v>
+        <v>6832758</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476424</v>
+        <v>129476422</v>
       </c>
       <c r="B46" t="n">
-        <v>97348</v>
+        <v>90585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497389</v>
+        <v>497310</v>
       </c>
       <c r="R46" t="n">
-        <v>6832716</v>
+        <v>6832692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476433</v>
+        <v>129476424</v>
       </c>
       <c r="B47" t="n">
-        <v>91606</v>
+        <v>97348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>2569</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497349</v>
+        <v>497389</v>
       </c>
       <c r="R47" t="n">
-        <v>6832759</v>
+        <v>6832716</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129465323</v>
+        <v>129476433</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497290</v>
+        <v>497349</v>
       </c>
       <c r="R48" t="n">
-        <v>6832699</v>
+        <v>6832759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B50" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R50" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B51" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R51" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476460</v>
+        <v>129476461</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497427</v>
+        <v>497297</v>
       </c>
       <c r="R52" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R53" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476434</v>
+        <v>129464078</v>
       </c>
       <c r="B54" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497367</v>
+        <v>497426</v>
       </c>
       <c r="R54" t="n">
-        <v>6832720</v>
+        <v>6832743</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5825,22 +5825,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476465</v>
+        <v>129466317</v>
       </c>
       <c r="B55" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,34 +5848,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497434</v>
+        <v>497335</v>
       </c>
       <c r="R55" t="n">
-        <v>6832759</v>
+        <v>6832765</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129466317</v>
+        <v>129476439</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,34 +5945,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497335</v>
+        <v>497415</v>
       </c>
       <c r="R56" t="n">
-        <v>6832765</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6019,22 +6019,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476439</v>
+        <v>129476465</v>
       </c>
       <c r="B57" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,21 +6042,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497415</v>
+        <v>497434</v>
       </c>
       <c r="R57" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129464078</v>
+        <v>129476434</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497426</v>
+        <v>497367</v>
       </c>
       <c r="R58" t="n">
-        <v>6832743</v>
+        <v>6832720</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6213,12 +6213,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129465171</v>
+        <v>129466545</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497309</v>
+        <v>497366</v>
       </c>
       <c r="R64" t="n">
-        <v>6832672</v>
+        <v>6832752</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129466545</v>
+        <v>129465171</v>
       </c>
       <c r="B65" t="n">
         <v>79044</v>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497366</v>
+        <v>497309</v>
       </c>
       <c r="R65" t="n">
-        <v>6832752</v>
+        <v>6832672</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7001,45 +7001,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129465586</v>
+        <v>129476431</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>92196</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>483</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497254</v>
+        <v>497392</v>
       </c>
       <c r="R67" t="n">
-        <v>6832729</v>
+        <v>6832754</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,57 +7086,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476431</v>
+        <v>129465586</v>
       </c>
       <c r="B68" t="n">
-        <v>92196</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>483</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497392</v>
+        <v>497254</v>
       </c>
       <c r="R68" t="n">
-        <v>6832754</v>
+        <v>6832729</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,12 +7183,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1079,7 +1079,7 @@
         <v>129476418</v>
       </c>
       <c r="B6" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R7" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476453</v>
+        <v>129465376</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,14 +1301,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497266</v>
+        <v>497292</v>
       </c>
       <c r="R8" t="n">
-        <v>6832713</v>
+        <v>6832709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,22 +1355,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129467135</v>
+        <v>129464751</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>90613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497389</v>
+        <v>497356</v>
       </c>
       <c r="R9" t="n">
-        <v>6832791</v>
+        <v>6832723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129464751</v>
+        <v>129467135</v>
       </c>
       <c r="B10" t="n">
-        <v>90585</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497356</v>
+        <v>497389</v>
       </c>
       <c r="R10" t="n">
-        <v>6832723</v>
+        <v>6832791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
         <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476427</v>
+        <v>129476462</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,42 +1669,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497307</v>
+        <v>497254</v>
       </c>
       <c r="R12" t="n">
-        <v>6832769</v>
+        <v>6832752</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129465572</v>
+        <v>129476464</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>78736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1774,34 +1766,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R13" t="n">
-        <v>6832729</v>
+        <v>6832724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,44 +1840,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476464</v>
+        <v>129476426</v>
       </c>
       <c r="B14" t="n">
-        <v>78710</v>
+        <v>97377</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1895,7 +1887,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497336</v>
+        <v>497413</v>
       </c>
       <c r="R14" t="n">
         <v>6832724</v>
@@ -1957,10 +1949,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476426</v>
+        <v>129476423</v>
       </c>
       <c r="B15" t="n">
-        <v>97348</v>
+        <v>97377</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497413</v>
+        <v>497256</v>
       </c>
       <c r="R15" t="n">
-        <v>6832724</v>
+        <v>6832740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476462</v>
+        <v>129476419</v>
       </c>
       <c r="B16" t="n">
-        <v>78710</v>
+        <v>79660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2089,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R16" t="n">
-        <v>6832752</v>
+        <v>6832679</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,45 +2143,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476423</v>
+        <v>129465572</v>
       </c>
       <c r="B17" t="n">
-        <v>97348</v>
+        <v>80175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497256</v>
+        <v>497254</v>
       </c>
       <c r="R17" t="n">
-        <v>6832740</v>
+        <v>6832729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,12 +2228,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2251,7 +2243,7 @@
         <v>129476428</v>
       </c>
       <c r="B18" t="n">
-        <v>92839</v>
+        <v>92867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476419</v>
+        <v>129476427</v>
       </c>
       <c r="B19" t="n">
-        <v>79634</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2356,34 +2348,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497336</v>
+        <v>497307</v>
       </c>
       <c r="R19" t="n">
-        <v>6832679</v>
+        <v>6832769</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
         <v>129476449</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129476457</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>129464182</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129476429</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129476437</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129464639</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129476417</v>
       </c>
       <c r="B26" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>129476454</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129476446</v>
       </c>
       <c r="B28" t="n">
-        <v>91726</v>
+        <v>91754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476450</v>
+        <v>129464293</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497272</v>
+        <v>497396</v>
       </c>
       <c r="R29" t="n">
-        <v>6832783</v>
+        <v>6832740</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476416</v>
+        <v>129476450</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497395</v>
+        <v>497272</v>
       </c>
       <c r="R30" t="n">
-        <v>6832737</v>
+        <v>6832783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129464293</v>
+        <v>129476416</v>
       </c>
       <c r="B31" t="n">
-        <v>78710</v>
+        <v>79689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,37 +3520,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497396</v>
+        <v>497395</v>
       </c>
       <c r="R31" t="n">
-        <v>6832740</v>
+        <v>6832737</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3594,12 +3594,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
         <v>129476430</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476466</v>
+        <v>129476435</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>78828</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497385</v>
+        <v>497301</v>
       </c>
       <c r="R33" t="n">
-        <v>6832779</v>
+        <v>6832764</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476435</v>
+        <v>129476451</v>
       </c>
       <c r="B34" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497301</v>
+        <v>497241</v>
       </c>
       <c r="R34" t="n">
-        <v>6832764</v>
+        <v>6832763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476451</v>
+        <v>129476452</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497241</v>
+        <v>497258</v>
       </c>
       <c r="R35" t="n">
-        <v>6832763</v>
+        <v>6832721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476452</v>
+        <v>129476466</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>92863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497258</v>
+        <v>497385</v>
       </c>
       <c r="R36" t="n">
-        <v>6832721</v>
+        <v>6832779</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78828</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R37" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B38" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R38" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476436</v>
+        <v>129476455</v>
       </c>
       <c r="B39" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497334</v>
+        <v>497307</v>
       </c>
       <c r="R39" t="n">
-        <v>6832674</v>
+        <v>6832696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476455</v>
+        <v>129476436</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78828</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497307</v>
+        <v>497334</v>
       </c>
       <c r="R40" t="n">
-        <v>6832696</v>
+        <v>6832674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
         <v>129464008</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>129476443</v>
       </c>
       <c r="B42" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>129465773</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129465323</v>
+        <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>90613</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497290</v>
+        <v>497336</v>
       </c>
       <c r="R44" t="n">
-        <v>6832699</v>
+        <v>6832758</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,22 +4855,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476421</v>
+        <v>129476422</v>
       </c>
       <c r="B45" t="n">
-        <v>90585</v>
+        <v>90613</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497336</v>
+        <v>497310</v>
       </c>
       <c r="R45" t="n">
-        <v>6832758</v>
+        <v>6832692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476422</v>
+        <v>129476433</v>
       </c>
       <c r="B46" t="n">
-        <v>90585</v>
+        <v>91634</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497310</v>
+        <v>497349</v>
       </c>
       <c r="R46" t="n">
-        <v>6832692</v>
+        <v>6832759</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5064,7 +5064,7 @@
         <v>129476424</v>
       </c>
       <c r="B47" t="n">
-        <v>97348</v>
+        <v>97377</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476433</v>
+        <v>129465323</v>
       </c>
       <c r="B48" t="n">
-        <v>91606</v>
+        <v>79070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497349</v>
+        <v>497290</v>
       </c>
       <c r="R48" t="n">
-        <v>6832759</v>
+        <v>6832699</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
         <v>129476415</v>
       </c>
       <c r="B49" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476460</v>
+        <v>129476461</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497427</v>
+        <v>497297</v>
       </c>
       <c r="R50" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R51" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R52" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R53" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5743,7 +5743,7 @@
         <v>129464078</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>129466317</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476439</v>
+        <v>129476465</v>
       </c>
       <c r="B56" t="n">
-        <v>78802</v>
+        <v>78736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,21 +5945,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497415</v>
+        <v>497434</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476465</v>
+        <v>129476434</v>
       </c>
       <c r="B57" t="n">
-        <v>78710</v>
+        <v>91634</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,21 +6042,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497434</v>
+        <v>497367</v>
       </c>
       <c r="R57" t="n">
-        <v>6832759</v>
+        <v>6832720</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476434</v>
+        <v>129463331</v>
       </c>
       <c r="B58" t="n">
-        <v>91606</v>
+        <v>58165</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>102999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497367</v>
+        <v>497447</v>
       </c>
       <c r="R58" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6213,22 +6213,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129463331</v>
+        <v>129476439</v>
       </c>
       <c r="B59" t="n">
-        <v>58162</v>
+        <v>78828</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,37 +6236,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102999</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497447</v>
+        <v>497415</v>
       </c>
       <c r="R59" t="n">
         <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,12 +6310,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
         <v>129476448</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>129476458</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>129476447</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476432</v>
+        <v>129466545</v>
       </c>
       <c r="B63" t="n">
-        <v>91606</v>
+        <v>79070</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497389</v>
+        <v>497366</v>
       </c>
       <c r="R63" t="n">
-        <v>6832749</v>
+        <v>6832752</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,22 +6698,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129466545</v>
+        <v>129465171</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497366</v>
+        <v>497309</v>
       </c>
       <c r="R64" t="n">
-        <v>6832752</v>
+        <v>6832672</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129465171</v>
+        <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>91634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497309</v>
+        <v>497389</v>
       </c>
       <c r="R65" t="n">
-        <v>6832672</v>
+        <v>6832749</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,22 +6892,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464850</v>
+        <v>129476420</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>79660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6915,34 +6915,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497345</v>
+        <v>497431</v>
       </c>
       <c r="R66" t="n">
-        <v>6832696</v>
+        <v>6832752</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,57 +6989,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129476431</v>
+        <v>129465586</v>
       </c>
       <c r="B67" t="n">
-        <v>92196</v>
+        <v>57890</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>483</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497392</v>
+        <v>497254</v>
       </c>
       <c r="R67" t="n">
-        <v>6832754</v>
+        <v>6832729</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,57 +7086,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129465586</v>
+        <v>129476431</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>92224</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>483</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497254</v>
+        <v>497392</v>
       </c>
       <c r="R68" t="n">
-        <v>6832729</v>
+        <v>6832754</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129476420</v>
+        <v>129464850</v>
       </c>
       <c r="B69" t="n">
-        <v>79634</v>
+        <v>79070</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497431</v>
+        <v>497345</v>
       </c>
       <c r="R69" t="n">
-        <v>6832752</v>
+        <v>6832696</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129464751</v>
+        <v>129467135</v>
       </c>
       <c r="B9" t="n">
-        <v>90613</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497356</v>
+        <v>497389</v>
       </c>
       <c r="R9" t="n">
-        <v>6832723</v>
+        <v>6832791</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129467135</v>
+        <v>129476442</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>78827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497389</v>
+        <v>497337</v>
       </c>
       <c r="R10" t="n">
-        <v>6832791</v>
+        <v>6832676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B11" t="n">
-        <v>78827</v>
+        <v>90613</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,12 +1646,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -5352,7 +5352,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476461</v>
+        <v>129476463</v>
       </c>
       <c r="B50" t="n">
         <v>78736</v>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497297</v>
+        <v>497356</v>
       </c>
       <c r="R50" t="n">
-        <v>6832767</v>
+        <v>6832686</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476463</v>
+        <v>129476461</v>
       </c>
       <c r="B51" t="n">
         <v>78736</v>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497356</v>
+        <v>497297</v>
       </c>
       <c r="R51" t="n">
-        <v>6832686</v>
+        <v>6832767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129464078</v>
+        <v>129476439</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>78828</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497426</v>
+        <v>497415</v>
       </c>
       <c r="R54" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5825,19 +5825,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129466317</v>
+        <v>129464078</v>
       </c>
       <c r="B55" t="n">
         <v>79070</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497335</v>
+        <v>497426</v>
       </c>
       <c r="R55" t="n">
-        <v>6832765</v>
+        <v>6832743</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476465</v>
+        <v>129466317</v>
       </c>
       <c r="B56" t="n">
-        <v>78736</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,34 +5945,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497434</v>
+        <v>497335</v>
       </c>
       <c r="R56" t="n">
-        <v>6832759</v>
+        <v>6832765</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6019,22 +6019,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476434</v>
+        <v>129476465</v>
       </c>
       <c r="B57" t="n">
-        <v>91634</v>
+        <v>78736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,21 +6042,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497367</v>
+        <v>497434</v>
       </c>
       <c r="R57" t="n">
-        <v>6832720</v>
+        <v>6832759</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129463331</v>
+        <v>129476434</v>
       </c>
       <c r="B58" t="n">
-        <v>58165</v>
+        <v>91634</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102999</v>
+        <v>2079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497447</v>
+        <v>497367</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6832720</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6213,22 +6213,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476439</v>
+        <v>129463331</v>
       </c>
       <c r="B59" t="n">
-        <v>78828</v>
+        <v>58165</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,37 +6236,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>102999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497415</v>
+        <v>497447</v>
       </c>
       <c r="R59" t="n">
         <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,12 +6310,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1079,7 +1079,7 @@
         <v>129476418</v>
       </c>
       <c r="B6" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476453</v>
+        <v>129465376</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497266</v>
+        <v>497292</v>
       </c>
       <c r="R7" t="n">
-        <v>6832713</v>
+        <v>6832709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,14 +1301,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R8" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,12 +1355,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
         <v>129467135</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>129476442</v>
       </c>
       <c r="B10" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>129464751</v>
       </c>
       <c r="B11" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,32 +1658,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476462</v>
+        <v>129476426</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>97389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497254</v>
+        <v>497413</v>
       </c>
       <c r="R12" t="n">
-        <v>6832752</v>
+        <v>6832724</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476464</v>
+        <v>129476423</v>
       </c>
       <c r="B13" t="n">
-        <v>78736</v>
+        <v>97389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497336</v>
+        <v>497256</v>
       </c>
       <c r="R13" t="n">
-        <v>6832724</v>
+        <v>6832740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,45 +1852,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476426</v>
+        <v>129476427</v>
       </c>
       <c r="B14" t="n">
-        <v>97377</v>
+        <v>57732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497413</v>
+        <v>497307</v>
       </c>
       <c r="R14" t="n">
-        <v>6832724</v>
+        <v>6832769</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,32 +1957,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476423</v>
+        <v>129476464</v>
       </c>
       <c r="B15" t="n">
-        <v>97377</v>
+        <v>78741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1984,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497256</v>
+        <v>497336</v>
       </c>
       <c r="R15" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476419</v>
+        <v>129476462</v>
       </c>
       <c r="B16" t="n">
-        <v>79660</v>
+        <v>78741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2065,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497336</v>
+        <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832679</v>
+        <v>6832752</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,45 +2151,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129465572</v>
+        <v>129476428</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>92873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497254</v>
+        <v>497387</v>
       </c>
       <c r="R17" t="n">
-        <v>6832729</v>
+        <v>6832781</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2228,57 +2236,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476428</v>
+        <v>129465572</v>
       </c>
       <c r="B18" t="n">
-        <v>92867</v>
+        <v>80180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497387</v>
+        <v>497254</v>
       </c>
       <c r="R18" t="n">
-        <v>6832781</v>
+        <v>6832729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2325,22 +2333,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476427</v>
+        <v>129476419</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79665</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,42 +2356,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497307</v>
+        <v>497336</v>
       </c>
       <c r="R19" t="n">
-        <v>6832769</v>
+        <v>6832679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
         <v>129476449</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129476457</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129464182</v>
+        <v>129476429</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>80181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497410</v>
+        <v>497288</v>
       </c>
       <c r="R22" t="n">
-        <v>6832744</v>
+        <v>6832771</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476429</v>
+        <v>129464182</v>
       </c>
       <c r="B23" t="n">
-        <v>80176</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497288</v>
+        <v>497410</v>
       </c>
       <c r="R23" t="n">
-        <v>6832771</v>
+        <v>6832744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,12 +2818,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
         <v>129476437</v>
       </c>
       <c r="B24" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129464639</v>
+        <v>129476417</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,34 +2938,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497352</v>
+        <v>497430</v>
       </c>
       <c r="R25" t="n">
-        <v>6832732</v>
+        <v>6832760</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,44 +3012,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476417</v>
+        <v>129476446</v>
       </c>
       <c r="B26" t="n">
-        <v>79689</v>
+        <v>91760</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497430</v>
+        <v>497331</v>
       </c>
       <c r="R26" t="n">
-        <v>6832760</v>
+        <v>6832758</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476454</v>
+        <v>129464639</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3152,14 +3152,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497292</v>
+        <v>497352</v>
       </c>
       <c r="R27" t="n">
-        <v>6832702</v>
+        <v>6832732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,44 +3206,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476446</v>
+        <v>129476454</v>
       </c>
       <c r="B28" t="n">
-        <v>91754</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497331</v>
+        <v>497292</v>
       </c>
       <c r="R28" t="n">
-        <v>6832758</v>
+        <v>6832702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
         <v>129464293</v>
       </c>
       <c r="B29" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476450</v>
+        <v>129476430</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>80181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497272</v>
+        <v>497250</v>
       </c>
       <c r="R30" t="n">
-        <v>6832783</v>
+        <v>6832730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
         <v>129476416</v>
       </c>
       <c r="B31" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476430</v>
+        <v>129476450</v>
       </c>
       <c r="B32" t="n">
-        <v>80176</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497250</v>
+        <v>497272</v>
       </c>
       <c r="R32" t="n">
-        <v>6832730</v>
+        <v>6832783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
         <v>129476435</v>
       </c>
       <c r="B33" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476451</v>
+        <v>129476466</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497241</v>
+        <v>497385</v>
       </c>
       <c r="R34" t="n">
-        <v>6832763</v>
+        <v>6832779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476452</v>
+        <v>129476451</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497258</v>
+        <v>497241</v>
       </c>
       <c r="R35" t="n">
-        <v>6832721</v>
+        <v>6832763</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476466</v>
+        <v>129476452</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>79075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497385</v>
+        <v>497258</v>
       </c>
       <c r="R36" t="n">
-        <v>6832779</v>
+        <v>6832721</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B37" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R37" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R38" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
         <v>129476455</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129476436</v>
       </c>
       <c r="B40" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R41" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,22 +4564,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476443</v>
+        <v>129464008</v>
       </c>
       <c r="B42" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497393</v>
+        <v>497425</v>
       </c>
       <c r="R42" t="n">
-        <v>6832735</v>
+        <v>6832750</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,12 +4661,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4676,7 +4676,7 @@
         <v>129465773</v>
       </c>
       <c r="B43" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129476422</v>
       </c>
       <c r="B45" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>129476433</v>
       </c>
       <c r="B46" t="n">
-        <v>91634</v>
+        <v>91640</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,45 +5061,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476424</v>
+        <v>129465323</v>
       </c>
       <c r="B47" t="n">
-        <v>97377</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497389</v>
+        <v>497290</v>
       </c>
       <c r="R47" t="n">
-        <v>6832716</v>
+        <v>6832699</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5146,57 +5146,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129465323</v>
+        <v>129476424</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>97389</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497290</v>
+        <v>497389</v>
       </c>
       <c r="R48" t="n">
-        <v>6832699</v>
+        <v>6832716</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
         <v>129476415</v>
       </c>
       <c r="B49" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476463</v>
+        <v>129476461</v>
       </c>
       <c r="B50" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497356</v>
+        <v>497297</v>
       </c>
       <c r="R50" t="n">
-        <v>6832686</v>
+        <v>6832767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476461</v>
+        <v>129476463</v>
       </c>
       <c r="B51" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497297</v>
+        <v>497356</v>
       </c>
       <c r="R51" t="n">
-        <v>6832767</v>
+        <v>6832686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5549,7 +5549,7 @@
         <v>129476460</v>
       </c>
       <c r="B52" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>129476456</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476439</v>
+        <v>129476465</v>
       </c>
       <c r="B54" t="n">
-        <v>78828</v>
+        <v>78741</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497415</v>
+        <v>497434</v>
       </c>
       <c r="R54" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129464078</v>
+        <v>129476434</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>91640</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,34 +5848,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497426</v>
+        <v>497367</v>
       </c>
       <c r="R55" t="n">
-        <v>6832743</v>
+        <v>6832720</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129466317</v>
+        <v>129464078</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497335</v>
+        <v>497426</v>
       </c>
       <c r="R56" t="n">
-        <v>6832765</v>
+        <v>6832743</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476465</v>
+        <v>129466317</v>
       </c>
       <c r="B57" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,34 +6042,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497434</v>
+        <v>497335</v>
       </c>
       <c r="R57" t="n">
-        <v>6832759</v>
+        <v>6832765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6116,22 +6116,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476434</v>
+        <v>129463331</v>
       </c>
       <c r="B58" t="n">
-        <v>91634</v>
+        <v>58170</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>102999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497367</v>
+        <v>497447</v>
       </c>
       <c r="R58" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6213,22 +6213,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129463331</v>
+        <v>129476439</v>
       </c>
       <c r="B59" t="n">
-        <v>58165</v>
+        <v>78833</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,37 +6236,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102999</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497447</v>
+        <v>497415</v>
       </c>
       <c r="R59" t="n">
         <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,12 +6310,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
         <v>129476448</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>129476458</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>129476447</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>129466545</v>
       </c>
       <c r="B63" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>129465171</v>
       </c>
       <c r="B64" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>91634</v>
+        <v>91640</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6904,32 +6904,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129476420</v>
+        <v>129476431</v>
       </c>
       <c r="B66" t="n">
-        <v>79660</v>
+        <v>92230</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>483</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497431</v>
+        <v>497392</v>
       </c>
       <c r="R66" t="n">
-        <v>6832752</v>
+        <v>6832754</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7004,7 +7004,7 @@
         <v>129465586</v>
       </c>
       <c r="B67" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,32 +7098,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476431</v>
+        <v>129476420</v>
       </c>
       <c r="B68" t="n">
-        <v>92224</v>
+        <v>79665</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>483</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497392</v>
+        <v>497431</v>
       </c>
       <c r="R68" t="n">
-        <v>6832754</v>
+        <v>6832752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7198,7 +7198,7 @@
         <v>129464850</v>
       </c>
       <c r="B69" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129476418</v>
+        <v>129465376</v>
       </c>
       <c r="B6" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497415</v>
+        <v>497292</v>
       </c>
       <c r="R6" t="n">
-        <v>6832767</v>
+        <v>6832709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,22 +1161,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R7" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476453</v>
+        <v>129476418</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497266</v>
+        <v>497415</v>
       </c>
       <c r="R8" t="n">
-        <v>6832713</v>
+        <v>6832767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
         <v>129467135</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B10" t="n">
-        <v>78832</v>
+        <v>90620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R10" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>90619</v>
+        <v>78833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R11" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,44 +1646,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476426</v>
+        <v>129476462</v>
       </c>
       <c r="B12" t="n">
-        <v>97389</v>
+        <v>78742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497413</v>
+        <v>497254</v>
       </c>
       <c r="R12" t="n">
-        <v>6832724</v>
+        <v>6832752</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476423</v>
+        <v>129476464</v>
       </c>
       <c r="B13" t="n">
-        <v>97389</v>
+        <v>78742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497256</v>
+        <v>497336</v>
       </c>
       <c r="R13" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
         <v>129476427</v>
       </c>
       <c r="B14" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,39 +1950,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476464</v>
+        <v>129476428</v>
       </c>
       <c r="B15" t="n">
-        <v>78741</v>
+        <v>92874</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497336</v>
+        <v>497387</v>
       </c>
       <c r="R15" t="n">
-        <v>6832724</v>
+        <v>6832781</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,39 +2047,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476462</v>
+        <v>129476426</v>
       </c>
       <c r="B16" t="n">
-        <v>78741</v>
+        <v>97390</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497254</v>
+        <v>497413</v>
       </c>
       <c r="R16" t="n">
-        <v>6832752</v>
+        <v>6832724</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,39 +2144,39 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476428</v>
+        <v>129476423</v>
       </c>
       <c r="B17" t="n">
-        <v>92873</v>
+        <v>97390</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497387</v>
+        <v>497256</v>
       </c>
       <c r="R17" t="n">
-        <v>6832781</v>
+        <v>6832740</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
         <v>129465572</v>
       </c>
       <c r="B18" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129476419</v>
       </c>
       <c r="B19" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
         <v>129476449</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129476457</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476429</v>
+        <v>129464182</v>
       </c>
       <c r="B22" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497288</v>
+        <v>497410</v>
       </c>
       <c r="R22" t="n">
-        <v>6832771</v>
+        <v>6832744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129464182</v>
+        <v>129476437</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497410</v>
+        <v>497395</v>
       </c>
       <c r="R23" t="n">
-        <v>6832744</v>
+        <v>6832737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,22 +2818,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476437</v>
+        <v>129476429</v>
       </c>
       <c r="B24" t="n">
-        <v>78833</v>
+        <v>80182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497395</v>
+        <v>497288</v>
       </c>
       <c r="R24" t="n">
-        <v>6832737</v>
+        <v>6832771</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2920,17 +2920,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476417</v>
+        <v>129464639</v>
       </c>
       <c r="B25" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,34 +2938,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497430</v>
+        <v>497352</v>
       </c>
       <c r="R25" t="n">
-        <v>6832760</v>
+        <v>6832732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,44 +3012,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476446</v>
+        <v>129476454</v>
       </c>
       <c r="B26" t="n">
-        <v>91760</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497331</v>
+        <v>497292</v>
       </c>
       <c r="R26" t="n">
-        <v>6832758</v>
+        <v>6832702</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,45 +3121,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129464639</v>
+        <v>129476446</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>91761</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497352</v>
+        <v>497331</v>
       </c>
       <c r="R27" t="n">
-        <v>6832732</v>
+        <v>6832758</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,22 +3206,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476454</v>
+        <v>129476417</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497292</v>
+        <v>497430</v>
       </c>
       <c r="R28" t="n">
-        <v>6832702</v>
+        <v>6832760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         <v>129464293</v>
       </c>
       <c r="B29" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129476430</v>
       </c>
       <c r="B30" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,17 +3502,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476416</v>
+        <v>129476450</v>
       </c>
       <c r="B31" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497395</v>
+        <v>497272</v>
       </c>
       <c r="R31" t="n">
-        <v>6832737</v>
+        <v>6832783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476450</v>
+        <v>129476416</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497272</v>
+        <v>497395</v>
       </c>
       <c r="R32" t="n">
-        <v>6832783</v>
+        <v>6832737</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,39 +3696,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476435</v>
+        <v>129476466</v>
       </c>
       <c r="B33" t="n">
-        <v>78833</v>
+        <v>92870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497301</v>
+        <v>497385</v>
       </c>
       <c r="R33" t="n">
-        <v>6832764</v>
+        <v>6832779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476466</v>
+        <v>129476451</v>
       </c>
       <c r="B34" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497385</v>
+        <v>497241</v>
       </c>
       <c r="R34" t="n">
-        <v>6832779</v>
+        <v>6832763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476451</v>
+        <v>129476452</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497241</v>
+        <v>497258</v>
       </c>
       <c r="R35" t="n">
-        <v>6832763</v>
+        <v>6832721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476452</v>
+        <v>129476435</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497258</v>
+        <v>497301</v>
       </c>
       <c r="R36" t="n">
-        <v>6832721</v>
+        <v>6832764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4094,7 +4094,7 @@
         <v>129476459</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>129476438</v>
       </c>
       <c r="B38" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
         <v>129476455</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129476436</v>
       </c>
       <c r="B40" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
         <v>129476443</v>
       </c>
       <c r="B41" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4579,7 +4579,7 @@
         <v>129464008</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>129465773</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476421</v>
+        <v>129465323</v>
       </c>
       <c r="B44" t="n">
-        <v>90619</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497336</v>
+        <v>497290</v>
       </c>
       <c r="R44" t="n">
-        <v>6832758</v>
+        <v>6832699</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,22 +4855,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476422</v>
+        <v>129476421</v>
       </c>
       <c r="B45" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497310</v>
+        <v>497336</v>
       </c>
       <c r="R45" t="n">
-        <v>6832692</v>
+        <v>6832758</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4957,17 +4957,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476433</v>
+        <v>129476422</v>
       </c>
       <c r="B46" t="n">
-        <v>91640</v>
+        <v>90620</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497349</v>
+        <v>497310</v>
       </c>
       <c r="R46" t="n">
-        <v>6832759</v>
+        <v>6832692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5054,52 +5054,52 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129465323</v>
+        <v>129476424</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>97390</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497290</v>
+        <v>497389</v>
       </c>
       <c r="R47" t="n">
-        <v>6832699</v>
+        <v>6832716</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5146,44 +5146,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476424</v>
+        <v>129476433</v>
       </c>
       <c r="B48" t="n">
-        <v>97389</v>
+        <v>91641</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2569</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497389</v>
+        <v>497349</v>
       </c>
       <c r="R48" t="n">
-        <v>6832716</v>
+        <v>6832759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
         <v>129476415</v>
       </c>
       <c r="B49" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5345,17 +5345,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B50" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R50" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B51" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R51" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476460</v>
+        <v>129476461</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497427</v>
+        <v>497297</v>
       </c>
       <c r="R52" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R53" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5743,7 +5743,7 @@
         <v>129476465</v>
       </c>
       <c r="B54" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476434</v>
+        <v>129463331</v>
       </c>
       <c r="B55" t="n">
-        <v>91640</v>
+        <v>58171</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,37 +5848,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2079</v>
+        <v>102999</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497367</v>
+        <v>497447</v>
       </c>
       <c r="R55" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129464078</v>
+        <v>129476439</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,34 +5945,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497426</v>
+        <v>497415</v>
       </c>
       <c r="R56" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6019,22 +6019,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129466317</v>
+        <v>129464078</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497335</v>
+        <v>497426</v>
       </c>
       <c r="R57" t="n">
-        <v>6832765</v>
+        <v>6832743</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129463331</v>
+        <v>129466317</v>
       </c>
       <c r="B58" t="n">
-        <v>58170</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,21 +6139,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102999</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497447</v>
+        <v>497335</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6832765</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6225,10 +6225,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476439</v>
+        <v>129476434</v>
       </c>
       <c r="B59" t="n">
-        <v>78833</v>
+        <v>91641</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,21 +6236,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497415</v>
+        <v>497367</v>
       </c>
       <c r="R59" t="n">
-        <v>6832767</v>
+        <v>6832720</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
         <v>129476448</v>
       </c>
       <c r="B60" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
         <v>129476458</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>129476447</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6616,7 +6616,7 @@
         <v>129466545</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>129465171</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>91640</v>
+        <v>91641</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6897,52 +6897,52 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129476431</v>
+        <v>129465586</v>
       </c>
       <c r="B66" t="n">
-        <v>92230</v>
+        <v>57896</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>483</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497392</v>
+        <v>497254</v>
       </c>
       <c r="R66" t="n">
-        <v>6832754</v>
+        <v>6832729</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,57 +6989,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129465586</v>
+        <v>129476431</v>
       </c>
       <c r="B67" t="n">
-        <v>57895</v>
+        <v>92231</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>483</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497254</v>
+        <v>497392</v>
       </c>
       <c r="R67" t="n">
-        <v>6832729</v>
+        <v>6832754</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,22 +7086,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476420</v>
+        <v>129464850</v>
       </c>
       <c r="B68" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7109,34 +7109,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497431</v>
+        <v>497345</v>
       </c>
       <c r="R68" t="n">
-        <v>6832752</v>
+        <v>6832696</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129464850</v>
+        <v>129476420</v>
       </c>
       <c r="B69" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497345</v>
+        <v>497431</v>
       </c>
       <c r="R69" t="n">
-        <v>6832696</v>
+        <v>6832752</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129464182</v>
+        <v>129476429</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>80182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497410</v>
+        <v>497288</v>
       </c>
       <c r="R22" t="n">
-        <v>6832744</v>
+        <v>6832771</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476437</v>
+        <v>129464182</v>
       </c>
       <c r="B23" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497395</v>
+        <v>497410</v>
       </c>
       <c r="R23" t="n">
-        <v>6832737</v>
+        <v>6832744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,22 +2818,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476429</v>
+        <v>129476437</v>
       </c>
       <c r="B24" t="n">
-        <v>80182</v>
+        <v>78834</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497288</v>
+        <v>497395</v>
       </c>
       <c r="R24" t="n">
-        <v>6832771</v>
+        <v>6832737</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476443</v>
+        <v>129464008</v>
       </c>
       <c r="B41" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497393</v>
+        <v>497425</v>
       </c>
       <c r="R41" t="n">
-        <v>6832735</v>
+        <v>6832750</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,19 +4564,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129464008</v>
+        <v>129465773</v>
       </c>
       <c r="B42" t="n">
         <v>79076</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497425</v>
+        <v>497256</v>
       </c>
       <c r="R42" t="n">
-        <v>6832750</v>
+        <v>6832783</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129465773</v>
+        <v>129476443</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4684,34 +4684,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497256</v>
+        <v>497393</v>
       </c>
       <c r="R43" t="n">
-        <v>6832783</v>
+        <v>6832735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4758,22 +4758,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129465323</v>
+        <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>90620</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497290</v>
+        <v>497336</v>
       </c>
       <c r="R44" t="n">
-        <v>6832699</v>
+        <v>6832758</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,19 +4855,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476421</v>
+        <v>129476422</v>
       </c>
       <c r="B45" t="n">
         <v>90620</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497336</v>
+        <v>497310</v>
       </c>
       <c r="R45" t="n">
-        <v>6832758</v>
+        <v>6832692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476422</v>
+        <v>129476424</v>
       </c>
       <c r="B46" t="n">
-        <v>90620</v>
+        <v>97390</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497310</v>
+        <v>497389</v>
       </c>
       <c r="R46" t="n">
-        <v>6832692</v>
+        <v>6832716</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476424</v>
+        <v>129476433</v>
       </c>
       <c r="B47" t="n">
-        <v>97390</v>
+        <v>91641</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2569</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497389</v>
+        <v>497349</v>
       </c>
       <c r="R47" t="n">
-        <v>6832716</v>
+        <v>6832759</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476433</v>
+        <v>129465323</v>
       </c>
       <c r="B48" t="n">
-        <v>91641</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497349</v>
+        <v>497290</v>
       </c>
       <c r="R48" t="n">
-        <v>6832759</v>
+        <v>6832699</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129465376</v>
+        <v>129476418</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497292</v>
+        <v>497415</v>
       </c>
       <c r="R6" t="n">
-        <v>6832709</v>
+        <v>6832767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,22 +1161,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476453</v>
+        <v>129465376</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497266</v>
+        <v>497292</v>
       </c>
       <c r="R7" t="n">
-        <v>6832713</v>
+        <v>6832709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476418</v>
+        <v>129476453</v>
       </c>
       <c r="B8" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497415</v>
+        <v>497266</v>
       </c>
       <c r="R8" t="n">
-        <v>6832767</v>
+        <v>6832713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129467135</v>
+        <v>129476442</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,34 +1378,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497389</v>
+        <v>497337</v>
       </c>
       <c r="R9" t="n">
-        <v>6832791</v>
+        <v>6832676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,22 +1452,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129464751</v>
+        <v>129467135</v>
       </c>
       <c r="B10" t="n">
-        <v>90620</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497356</v>
+        <v>497389</v>
       </c>
       <c r="R10" t="n">
-        <v>6832723</v>
+        <v>6832791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B11" t="n">
-        <v>78833</v>
+        <v>90625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,22 +1646,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476462</v>
+        <v>129476464</v>
       </c>
       <c r="B12" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R12" t="n">
-        <v>6832752</v>
+        <v>6832724</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476464</v>
+        <v>129476462</v>
       </c>
       <c r="B13" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497336</v>
+        <v>497254</v>
       </c>
       <c r="R13" t="n">
-        <v>6832724</v>
+        <v>6832752</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,53 +1852,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476427</v>
+        <v>129476426</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>97395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497307</v>
+        <v>497413</v>
       </c>
       <c r="R14" t="n">
-        <v>6832769</v>
+        <v>6832724</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,39 +1942,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476428</v>
+        <v>129476423</v>
       </c>
       <c r="B15" t="n">
-        <v>92874</v>
+        <v>97395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497387</v>
+        <v>497256</v>
       </c>
       <c r="R15" t="n">
-        <v>6832781</v>
+        <v>6832740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,52 +2039,52 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476426</v>
+        <v>129465572</v>
       </c>
       <c r="B16" t="n">
-        <v>97390</v>
+        <v>80186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497413</v>
+        <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832724</v>
+        <v>6832729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,44 +2131,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476423</v>
+        <v>129476428</v>
       </c>
       <c r="B17" t="n">
-        <v>97390</v>
+        <v>92879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2186,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497256</v>
+        <v>497387</v>
       </c>
       <c r="R17" t="n">
-        <v>6832740</v>
+        <v>6832781</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,17 +2233,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129465572</v>
+        <v>129476427</v>
       </c>
       <c r="B18" t="n">
-        <v>80181</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2259,34 +2251,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497254</v>
+        <v>497307</v>
       </c>
       <c r="R18" t="n">
-        <v>6832729</v>
+        <v>6832769</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,12 +2333,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
         <v>129476419</v>
       </c>
       <c r="B19" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
         <v>129476449</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129476457</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>129476429</v>
       </c>
       <c r="B22" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
         <v>129464182</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129476437</v>
       </c>
       <c r="B24" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2920,52 +2920,52 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129464639</v>
+        <v>129476446</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>91766</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497352</v>
+        <v>497331</v>
       </c>
       <c r="R25" t="n">
-        <v>6832732</v>
+        <v>6832758</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,22 +3012,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476454</v>
+        <v>129476417</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497292</v>
+        <v>497430</v>
       </c>
       <c r="R26" t="n">
-        <v>6832702</v>
+        <v>6832760</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,45 +3121,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476446</v>
+        <v>129464639</v>
       </c>
       <c r="B27" t="n">
-        <v>91761</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497331</v>
+        <v>497352</v>
       </c>
       <c r="R27" t="n">
-        <v>6832758</v>
+        <v>6832732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,22 +3206,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476417</v>
+        <v>129476454</v>
       </c>
       <c r="B28" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497430</v>
+        <v>497292</v>
       </c>
       <c r="R28" t="n">
-        <v>6832760</v>
+        <v>6832702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         <v>129464293</v>
       </c>
       <c r="B29" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129476430</v>
       </c>
       <c r="B30" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,17 +3502,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476450</v>
+        <v>129476416</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497272</v>
+        <v>497395</v>
       </c>
       <c r="R31" t="n">
-        <v>6832783</v>
+        <v>6832737</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476416</v>
+        <v>129476450</v>
       </c>
       <c r="B32" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497395</v>
+        <v>497272</v>
       </c>
       <c r="R32" t="n">
-        <v>6832737</v>
+        <v>6832783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,39 +3696,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476466</v>
+        <v>129476452</v>
       </c>
       <c r="B33" t="n">
-        <v>92870</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497385</v>
+        <v>497258</v>
       </c>
       <c r="R33" t="n">
-        <v>6832779</v>
+        <v>6832721</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3803,7 +3803,7 @@
         <v>129476451</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476452</v>
+        <v>129476466</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>92875</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497258</v>
+        <v>497385</v>
       </c>
       <c r="R35" t="n">
-        <v>6832721</v>
+        <v>6832779</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
         <v>129476435</v>
       </c>
       <c r="B36" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4094,7 +4094,7 @@
         <v>129476459</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>129476438</v>
       </c>
       <c r="B38" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
         <v>129476455</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129476436</v>
       </c>
       <c r="B40" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R41" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,12 +4564,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4579,7 +4579,7 @@
         <v>129465773</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476443</v>
+        <v>129464008</v>
       </c>
       <c r="B43" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4684,34 +4684,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497393</v>
+        <v>497425</v>
       </c>
       <c r="R43" t="n">
-        <v>6832735</v>
+        <v>6832750</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4758,12 +4758,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
         <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -4870,7 +4870,7 @@
         <v>129476422</v>
       </c>
       <c r="B45" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
         <v>129476424</v>
       </c>
       <c r="B46" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5064,7 +5064,7 @@
         <v>129476433</v>
       </c>
       <c r="B47" t="n">
-        <v>91641</v>
+        <v>91646</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5161,7 +5161,7 @@
         <v>129465323</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>129476415</v>
       </c>
       <c r="B49" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5345,17 +5345,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476460</v>
+        <v>129476456</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497427</v>
+        <v>497344</v>
       </c>
       <c r="R50" t="n">
-        <v>6832743</v>
+        <v>6832689</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476456</v>
+        <v>129476460</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497344</v>
+        <v>497427</v>
       </c>
       <c r="R51" t="n">
-        <v>6832689</v>
+        <v>6832743</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5549,7 +5549,7 @@
         <v>129476461</v>
       </c>
       <c r="B52" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>129476463</v>
       </c>
       <c r="B53" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476465</v>
+        <v>129476439</v>
       </c>
       <c r="B54" t="n">
-        <v>78742</v>
+        <v>78839</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497434</v>
+        <v>497415</v>
       </c>
       <c r="R54" t="n">
-        <v>6832759</v>
+        <v>6832767</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129463331</v>
+        <v>129476465</v>
       </c>
       <c r="B55" t="n">
-        <v>58171</v>
+        <v>78747</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,37 +5848,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102999</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497447</v>
+        <v>497434</v>
       </c>
       <c r="R55" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476439</v>
+        <v>129476434</v>
       </c>
       <c r="B56" t="n">
-        <v>78834</v>
+        <v>91646</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,21 +5945,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497415</v>
+        <v>497367</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6832720</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6024,17 +6024,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129464078</v>
+        <v>129466317</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497426</v>
+        <v>497335</v>
       </c>
       <c r="R57" t="n">
-        <v>6832743</v>
+        <v>6832765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129466317</v>
+        <v>129464078</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497335</v>
+        <v>497426</v>
       </c>
       <c r="R58" t="n">
-        <v>6832765</v>
+        <v>6832743</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6225,10 +6225,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476434</v>
+        <v>129463331</v>
       </c>
       <c r="B59" t="n">
-        <v>91641</v>
+        <v>58171</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,37 +6236,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2079</v>
+        <v>102999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497367</v>
+        <v>497447</v>
       </c>
       <c r="R59" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,22 +6310,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476448</v>
+        <v>129476447</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497361</v>
+        <v>497367</v>
       </c>
       <c r="R60" t="n">
-        <v>6832760</v>
+        <v>6832744</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
         <v>129476458</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476447</v>
+        <v>129476448</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497367</v>
+        <v>497361</v>
       </c>
       <c r="R62" t="n">
-        <v>6832744</v>
+        <v>6832760</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,17 +6606,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129466545</v>
+        <v>129476432</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>91646</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497366</v>
+        <v>497389</v>
       </c>
       <c r="R63" t="n">
-        <v>6832752</v>
+        <v>6832749</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,22 +6698,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129465171</v>
+        <v>129466545</v>
       </c>
       <c r="B64" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497309</v>
+        <v>497366</v>
       </c>
       <c r="R64" t="n">
-        <v>6832672</v>
+        <v>6832752</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129476432</v>
+        <v>129465171</v>
       </c>
       <c r="B65" t="n">
-        <v>91641</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497389</v>
+        <v>497309</v>
       </c>
       <c r="R65" t="n">
-        <v>6832749</v>
+        <v>6832672</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,22 +6892,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129465586</v>
+        <v>129464850</v>
       </c>
       <c r="B66" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6915,21 +6915,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497254</v>
+        <v>497345</v>
       </c>
       <c r="R66" t="n">
-        <v>6832729</v>
+        <v>6832696</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7001,32 +7001,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129476431</v>
+        <v>129476420</v>
       </c>
       <c r="B67" t="n">
-        <v>92231</v>
+        <v>79671</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>483</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497392</v>
+        <v>497431</v>
       </c>
       <c r="R67" t="n">
-        <v>6832754</v>
+        <v>6832752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7091,52 +7091,52 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129464850</v>
+        <v>129476431</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>92236</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497345</v>
+        <v>497392</v>
       </c>
       <c r="R68" t="n">
-        <v>6832696</v>
+        <v>6832754</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129476420</v>
+        <v>129465586</v>
       </c>
       <c r="B69" t="n">
-        <v>79666</v>
+        <v>57896</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497431</v>
+        <v>497254</v>
       </c>
       <c r="R69" t="n">
-        <v>6832752</v>
+        <v>6832729</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129476418</v>
+        <v>129465376</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497415</v>
+        <v>497292</v>
       </c>
       <c r="R6" t="n">
-        <v>6832767</v>
+        <v>6832709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1161,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R7" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476453</v>
+        <v>129476418</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497266</v>
+        <v>497415</v>
       </c>
       <c r="R8" t="n">
-        <v>6832713</v>
+        <v>6832767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129476442</v>
+        <v>129467135</v>
       </c>
       <c r="B9" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,34 +1378,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497337</v>
+        <v>497389</v>
       </c>
       <c r="R9" t="n">
-        <v>6832676</v>
+        <v>6832791</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,22 +1452,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129467135</v>
+        <v>129464751</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>90625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497389</v>
+        <v>497356</v>
       </c>
       <c r="R10" t="n">
-        <v>6832791</v>
+        <v>6832723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>90625</v>
+        <v>78838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R11" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,44 +1646,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476464</v>
+        <v>129476423</v>
       </c>
       <c r="B12" t="n">
-        <v>78747</v>
+        <v>97395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497336</v>
+        <v>497256</v>
       </c>
       <c r="R12" t="n">
-        <v>6832724</v>
+        <v>6832740</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476462</v>
+        <v>129476426</v>
       </c>
       <c r="B13" t="n">
-        <v>78747</v>
+        <v>97395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497254</v>
+        <v>497413</v>
       </c>
       <c r="R13" t="n">
-        <v>6832752</v>
+        <v>6832724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476426</v>
+        <v>129476462</v>
       </c>
       <c r="B14" t="n">
-        <v>97395</v>
+        <v>78747</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497413</v>
+        <v>497254</v>
       </c>
       <c r="R14" t="n">
-        <v>6832724</v>
+        <v>6832752</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,45 +1949,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476423</v>
+        <v>129465572</v>
       </c>
       <c r="B15" t="n">
-        <v>97395</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497256</v>
+        <v>497254</v>
       </c>
       <c r="R15" t="n">
-        <v>6832740</v>
+        <v>6832729</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2034,22 +2034,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129465572</v>
+        <v>129476427</v>
       </c>
       <c r="B16" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,34 +2057,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497254</v>
+        <v>497307</v>
       </c>
       <c r="R16" t="n">
-        <v>6832729</v>
+        <v>6832769</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2131,44 +2139,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476428</v>
+        <v>129476419</v>
       </c>
       <c r="B17" t="n">
-        <v>92879</v>
+        <v>79671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2186,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497387</v>
+        <v>497336</v>
       </c>
       <c r="R17" t="n">
-        <v>6832781</v>
+        <v>6832679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,10 +2248,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476427</v>
+        <v>129476464</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>78747</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,42 +2259,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497307</v>
+        <v>497336</v>
       </c>
       <c r="R18" t="n">
-        <v>6832769</v>
+        <v>6832724</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,32 +2345,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476419</v>
+        <v>129476428</v>
       </c>
       <c r="B19" t="n">
-        <v>79671</v>
+        <v>92879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497336</v>
+        <v>497387</v>
       </c>
       <c r="R19" t="n">
-        <v>6832679</v>
+        <v>6832781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476417</v>
+        <v>129476454</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497430</v>
+        <v>497292</v>
       </c>
       <c r="R26" t="n">
-        <v>6832760</v>
+        <v>6832702</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129464639</v>
+        <v>129476417</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,34 +3132,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497352</v>
+        <v>497430</v>
       </c>
       <c r="R27" t="n">
-        <v>6832732</v>
+        <v>6832760</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,19 +3206,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476454</v>
+        <v>129464639</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3249,14 +3249,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497292</v>
+        <v>497352</v>
       </c>
       <c r="R28" t="n">
-        <v>6832702</v>
+        <v>6832732</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3303,22 +3303,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129464293</v>
+        <v>129476430</v>
       </c>
       <c r="B29" t="n">
-        <v>78747</v>
+        <v>80187</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497396</v>
+        <v>497250</v>
       </c>
       <c r="R29" t="n">
-        <v>6832740</v>
+        <v>6832730</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476430</v>
+        <v>129464293</v>
       </c>
       <c r="B30" t="n">
-        <v>80187</v>
+        <v>78747</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,37 +3423,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497250</v>
+        <v>497396</v>
       </c>
       <c r="R30" t="n">
-        <v>6832730</v>
+        <v>6832740</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3497,22 +3497,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476416</v>
+        <v>129476450</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497395</v>
+        <v>497272</v>
       </c>
       <c r="R31" t="n">
-        <v>6832737</v>
+        <v>6832783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476450</v>
+        <v>129476416</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497272</v>
+        <v>497395</v>
       </c>
       <c r="R32" t="n">
-        <v>6832783</v>
+        <v>6832737</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476452</v>
+        <v>129476451</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497258</v>
+        <v>497241</v>
       </c>
       <c r="R33" t="n">
-        <v>6832721</v>
+        <v>6832763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476451</v>
+        <v>129476452</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497241</v>
+        <v>497258</v>
       </c>
       <c r="R34" t="n">
-        <v>6832763</v>
+        <v>6832721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476466</v>
+        <v>129476435</v>
       </c>
       <c r="B35" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497385</v>
+        <v>497301</v>
       </c>
       <c r="R35" t="n">
-        <v>6832779</v>
+        <v>6832764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476435</v>
+        <v>129476466</v>
       </c>
       <c r="B36" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497301</v>
+        <v>497385</v>
       </c>
       <c r="R36" t="n">
-        <v>6832764</v>
+        <v>6832779</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R37" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R38" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476443</v>
+        <v>129464008</v>
       </c>
       <c r="B41" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497393</v>
+        <v>497425</v>
       </c>
       <c r="R41" t="n">
-        <v>6832735</v>
+        <v>6832750</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,22 +4564,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129465773</v>
+        <v>129476443</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497256</v>
+        <v>497393</v>
       </c>
       <c r="R42" t="n">
-        <v>6832783</v>
+        <v>6832735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,19 +4661,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129464008</v>
+        <v>129465773</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497425</v>
+        <v>497256</v>
       </c>
       <c r="R43" t="n">
-        <v>6832750</v>
+        <v>6832783</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4770,32 +4770,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476421</v>
+        <v>129476424</v>
       </c>
       <c r="B44" t="n">
-        <v>90625</v>
+        <v>97395</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>2569</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497336</v>
+        <v>497389</v>
       </c>
       <c r="R44" t="n">
-        <v>6832758</v>
+        <v>6832716</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,32 +4964,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476424</v>
+        <v>129476421</v>
       </c>
       <c r="B46" t="n">
-        <v>97395</v>
+        <v>90625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497389</v>
+        <v>497336</v>
       </c>
       <c r="R46" t="n">
-        <v>6832716</v>
+        <v>6832758</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476456</v>
+        <v>129476461</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497344</v>
+        <v>497297</v>
       </c>
       <c r="R50" t="n">
-        <v>6832689</v>
+        <v>6832767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476460</v>
+        <v>129476463</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497427</v>
+        <v>497356</v>
       </c>
       <c r="R51" t="n">
-        <v>6832743</v>
+        <v>6832686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B52" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R52" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B53" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R53" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476439</v>
+        <v>129476465</v>
       </c>
       <c r="B54" t="n">
-        <v>78839</v>
+        <v>78747</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497415</v>
+        <v>497434</v>
       </c>
       <c r="R54" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476465</v>
+        <v>129463331</v>
       </c>
       <c r="B55" t="n">
-        <v>78747</v>
+        <v>58171</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,37 +5848,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>102999</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497434</v>
+        <v>497447</v>
       </c>
       <c r="R55" t="n">
-        <v>6832759</v>
+        <v>6832767</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5922,12 +5922,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129466317</v>
+        <v>129464078</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497335</v>
+        <v>497426</v>
       </c>
       <c r="R57" t="n">
-        <v>6832765</v>
+        <v>6832743</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129464078</v>
+        <v>129466317</v>
       </c>
       <c r="B58" t="n">
         <v>79081</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497426</v>
+        <v>497335</v>
       </c>
       <c r="R58" t="n">
-        <v>6832743</v>
+        <v>6832765</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6225,10 +6225,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129463331</v>
+        <v>129476439</v>
       </c>
       <c r="B59" t="n">
-        <v>58171</v>
+        <v>78839</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,37 +6236,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102999</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497447</v>
+        <v>497415</v>
       </c>
       <c r="R59" t="n">
         <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,19 +6310,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476447</v>
+        <v>129476448</v>
       </c>
       <c r="B60" t="n">
         <v>79081</v>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497367</v>
+        <v>497361</v>
       </c>
       <c r="R60" t="n">
-        <v>6832744</v>
+        <v>6832760</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476448</v>
+        <v>129476447</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497361</v>
+        <v>497367</v>
       </c>
       <c r="R62" t="n">
-        <v>6832760</v>
+        <v>6832744</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476432</v>
+        <v>129466545</v>
       </c>
       <c r="B63" t="n">
-        <v>91646</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497389</v>
+        <v>497366</v>
       </c>
       <c r="R63" t="n">
-        <v>6832749</v>
+        <v>6832752</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,19 +6698,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129466545</v>
+        <v>129465171</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497366</v>
+        <v>497309</v>
       </c>
       <c r="R64" t="n">
-        <v>6832752</v>
+        <v>6832672</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129465171</v>
+        <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>91646</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497309</v>
+        <v>497389</v>
       </c>
       <c r="R65" t="n">
-        <v>6832672</v>
+        <v>6832749</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,57 +6892,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464850</v>
+        <v>129476431</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>92236</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497345</v>
+        <v>497392</v>
       </c>
       <c r="R66" t="n">
-        <v>6832696</v>
+        <v>6832754</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,22 +6989,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129476420</v>
+        <v>129465586</v>
       </c>
       <c r="B67" t="n">
-        <v>79671</v>
+        <v>57896</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497431</v>
+        <v>497254</v>
       </c>
       <c r="R67" t="n">
-        <v>6832752</v>
+        <v>6832729</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,44 +7086,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476431</v>
+        <v>129476420</v>
       </c>
       <c r="B68" t="n">
-        <v>92236</v>
+        <v>79671</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>483</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497392</v>
+        <v>497431</v>
       </c>
       <c r="R68" t="n">
-        <v>6832754</v>
+        <v>6832752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7195,10 +7195,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129465586</v>
+        <v>129464850</v>
       </c>
       <c r="B69" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,21 +7206,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497254</v>
+        <v>497345</v>
       </c>
       <c r="R69" t="n">
-        <v>6832729</v>
+        <v>6832696</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,7 +1076,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1107,14 +1107,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R6" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1161,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476453</v>
+        <v>129465376</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497266</v>
+        <v>497292</v>
       </c>
       <c r="R7" t="n">
-        <v>6832713</v>
+        <v>6832709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,12 +1258,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B10" t="n">
-        <v>90625</v>
+        <v>78838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R10" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B11" t="n">
-        <v>78838</v>
+        <v>90625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,12 +1646,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476426</v>
+        <v>129476464</v>
       </c>
       <c r="B13" t="n">
-        <v>97395</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497413</v>
+        <v>497336</v>
       </c>
       <c r="R13" t="n">
         <v>6832724</v>
@@ -1949,45 +1949,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129465572</v>
+        <v>129476428</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>92879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497254</v>
+        <v>497387</v>
       </c>
       <c r="R15" t="n">
-        <v>6832729</v>
+        <v>6832781</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2034,22 +2034,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476427</v>
+        <v>129465572</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>80186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,42 +2057,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497307</v>
+        <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832769</v>
+        <v>6832729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,12 +2131,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2248,32 +2240,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476464</v>
+        <v>129476426</v>
       </c>
       <c r="B18" t="n">
-        <v>78747</v>
+        <v>97395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,7 +2275,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497336</v>
+        <v>497413</v>
       </c>
       <c r="R18" t="n">
         <v>6832724</v>
@@ -2345,45 +2337,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476428</v>
+        <v>129476427</v>
       </c>
       <c r="B19" t="n">
-        <v>92879</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497387</v>
+        <v>497307</v>
       </c>
       <c r="R19" t="n">
-        <v>6832781</v>
+        <v>6832769</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476454</v>
+        <v>129464639</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3055,14 +3055,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497292</v>
+        <v>497352</v>
       </c>
       <c r="R26" t="n">
-        <v>6832702</v>
+        <v>6832732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,22 +3109,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476417</v>
+        <v>129476454</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497430</v>
+        <v>497292</v>
       </c>
       <c r="R27" t="n">
-        <v>6832760</v>
+        <v>6832702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129464639</v>
+        <v>129476417</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,34 +3229,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497352</v>
+        <v>497430</v>
       </c>
       <c r="R28" t="n">
-        <v>6832732</v>
+        <v>6832760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3303,22 +3303,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476430</v>
+        <v>129464293</v>
       </c>
       <c r="B29" t="n">
-        <v>80187</v>
+        <v>78747</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,37 +3326,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497250</v>
+        <v>497396</v>
       </c>
       <c r="R29" t="n">
-        <v>6832730</v>
+        <v>6832740</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3400,22 +3400,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129464293</v>
+        <v>129476450</v>
       </c>
       <c r="B30" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,37 +3423,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497396</v>
+        <v>497272</v>
       </c>
       <c r="R30" t="n">
-        <v>6832740</v>
+        <v>6832783</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3497,22 +3497,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476450</v>
+        <v>129476430</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497272</v>
+        <v>497250</v>
       </c>
       <c r="R31" t="n">
-        <v>6832783</v>
+        <v>6832730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476435</v>
+        <v>129476466</v>
       </c>
       <c r="B35" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497301</v>
+        <v>497385</v>
       </c>
       <c r="R35" t="n">
-        <v>6832764</v>
+        <v>6832779</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476466</v>
+        <v>129476435</v>
       </c>
       <c r="B36" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497385</v>
+        <v>497301</v>
       </c>
       <c r="R36" t="n">
-        <v>6832779</v>
+        <v>6832764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476438</v>
+        <v>129476459</v>
       </c>
       <c r="B37" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497401</v>
+        <v>497362</v>
       </c>
       <c r="R37" t="n">
-        <v>6832738</v>
+        <v>6832731</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476459</v>
+        <v>129476438</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497362</v>
+        <v>497401</v>
       </c>
       <c r="R38" t="n">
-        <v>6832731</v>
+        <v>6832738</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476422</v>
+        <v>129476433</v>
       </c>
       <c r="B45" t="n">
-        <v>90625</v>
+        <v>91646</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497310</v>
+        <v>497349</v>
       </c>
       <c r="R45" t="n">
-        <v>6832692</v>
+        <v>6832759</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476433</v>
+        <v>129476422</v>
       </c>
       <c r="B47" t="n">
-        <v>91646</v>
+        <v>90625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497349</v>
+        <v>497310</v>
       </c>
       <c r="R47" t="n">
-        <v>6832759</v>
+        <v>6832692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476465</v>
+        <v>129476434</v>
       </c>
       <c r="B54" t="n">
-        <v>78747</v>
+        <v>91646</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497434</v>
+        <v>497367</v>
       </c>
       <c r="R54" t="n">
-        <v>6832759</v>
+        <v>6832720</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129463331</v>
+        <v>129476465</v>
       </c>
       <c r="B55" t="n">
-        <v>58171</v>
+        <v>78747</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,37 +5848,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102999</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497447</v>
+        <v>497434</v>
       </c>
       <c r="R55" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5922,22 +5922,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476434</v>
+        <v>129464078</v>
       </c>
       <c r="B56" t="n">
-        <v>91646</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,34 +5945,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497367</v>
+        <v>497426</v>
       </c>
       <c r="R56" t="n">
-        <v>6832720</v>
+        <v>6832743</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6019,19 +6019,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129464078</v>
+        <v>129466317</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497426</v>
+        <v>497335</v>
       </c>
       <c r="R57" t="n">
-        <v>6832743</v>
+        <v>6832765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129466317</v>
+        <v>129463331</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>58171</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,21 +6139,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>102999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497335</v>
+        <v>497447</v>
       </c>
       <c r="R58" t="n">
-        <v>6832765</v>
+        <v>6832767</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129465586</v>
+        <v>129464850</v>
       </c>
       <c r="B67" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497254</v>
+        <v>497345</v>
       </c>
       <c r="R67" t="n">
-        <v>6832729</v>
+        <v>6832696</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476420</v>
+        <v>129465586</v>
       </c>
       <c r="B68" t="n">
-        <v>79671</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7109,34 +7109,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497431</v>
+        <v>497254</v>
       </c>
       <c r="R68" t="n">
-        <v>6832752</v>
+        <v>6832729</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129464850</v>
+        <v>129476420</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497345</v>
+        <v>497431</v>
       </c>
       <c r="R69" t="n">
-        <v>6832696</v>
+        <v>6832752</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,7 +1076,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129476453</v>
+        <v>129465376</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1107,14 +1107,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497266</v>
+        <v>497292</v>
       </c>
       <c r="R6" t="n">
-        <v>6832713</v>
+        <v>6832709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1161,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129465376</v>
+        <v>129476453</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497292</v>
+        <v>497266</v>
       </c>
       <c r="R7" t="n">
-        <v>6832709</v>
+        <v>6832713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,12 +1258,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129467135</v>
+        <v>129464751</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>90625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497389</v>
+        <v>497356</v>
       </c>
       <c r="R9" t="n">
-        <v>6832791</v>
+        <v>6832723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476442</v>
+        <v>129467135</v>
       </c>
       <c r="B10" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497337</v>
+        <v>497389</v>
       </c>
       <c r="R10" t="n">
-        <v>6832676</v>
+        <v>6832791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>90625</v>
+        <v>78838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R11" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476423</v>
+        <v>129476426</v>
       </c>
       <c r="B12" t="n">
         <v>97395</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497256</v>
+        <v>497413</v>
       </c>
       <c r="R12" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476464</v>
+        <v>129476423</v>
       </c>
       <c r="B13" t="n">
-        <v>78747</v>
+        <v>97395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497336</v>
+        <v>497256</v>
       </c>
       <c r="R13" t="n">
-        <v>6832724</v>
+        <v>6832740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476462</v>
+        <v>129476427</v>
       </c>
       <c r="B14" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,34 +1863,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497254</v>
+        <v>497307</v>
       </c>
       <c r="R14" t="n">
-        <v>6832752</v>
+        <v>6832769</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,32 +1957,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476428</v>
+        <v>129476464</v>
       </c>
       <c r="B15" t="n">
-        <v>92879</v>
+        <v>78747</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1984,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497387</v>
+        <v>497336</v>
       </c>
       <c r="R15" t="n">
-        <v>6832781</v>
+        <v>6832724</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129465572</v>
+        <v>129476462</v>
       </c>
       <c r="B16" t="n">
-        <v>80186</v>
+        <v>78747</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,34 +2065,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832729</v>
+        <v>6832752</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2131,44 +2139,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476419</v>
+        <v>129476428</v>
       </c>
       <c r="B17" t="n">
-        <v>79671</v>
+        <v>92879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2186,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497336</v>
+        <v>497387</v>
       </c>
       <c r="R17" t="n">
-        <v>6832679</v>
+        <v>6832781</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,45 +2248,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476426</v>
+        <v>129465572</v>
       </c>
       <c r="B18" t="n">
-        <v>97395</v>
+        <v>80186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497413</v>
+        <v>497254</v>
       </c>
       <c r="R18" t="n">
-        <v>6832724</v>
+        <v>6832729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2325,22 +2333,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476427</v>
+        <v>129476419</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,42 +2356,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497307</v>
+        <v>497336</v>
       </c>
       <c r="R19" t="n">
-        <v>6832769</v>
+        <v>6832679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476429</v>
+        <v>129464182</v>
       </c>
       <c r="B22" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497288</v>
+        <v>497410</v>
       </c>
       <c r="R22" t="n">
-        <v>6832771</v>
+        <v>6832744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129464182</v>
+        <v>129476429</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497410</v>
+        <v>497288</v>
       </c>
       <c r="R23" t="n">
-        <v>6832744</v>
+        <v>6832771</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,12 +2818,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2927,32 +2927,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476446</v>
+        <v>129476417</v>
       </c>
       <c r="B25" t="n">
-        <v>91766</v>
+        <v>79700</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497331</v>
+        <v>497430</v>
       </c>
       <c r="R25" t="n">
-        <v>6832758</v>
+        <v>6832760</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3024,45 +3024,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129464639</v>
+        <v>129476446</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>91766</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497352</v>
+        <v>497331</v>
       </c>
       <c r="R26" t="n">
-        <v>6832732</v>
+        <v>6832758</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,19 +3109,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476454</v>
+        <v>129464639</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3152,14 +3152,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497292</v>
+        <v>497352</v>
       </c>
       <c r="R27" t="n">
-        <v>6832702</v>
+        <v>6832732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,22 +3206,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476417</v>
+        <v>129476454</v>
       </c>
       <c r="B28" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497430</v>
+        <v>497292</v>
       </c>
       <c r="R28" t="n">
-        <v>6832760</v>
+        <v>6832702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476450</v>
+        <v>129476430</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497272</v>
+        <v>497250</v>
       </c>
       <c r="R30" t="n">
-        <v>6832783</v>
+        <v>6832730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476430</v>
+        <v>129476416</v>
       </c>
       <c r="B31" t="n">
-        <v>80187</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497250</v>
+        <v>497395</v>
       </c>
       <c r="R31" t="n">
-        <v>6832730</v>
+        <v>6832737</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476416</v>
+        <v>129476450</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497395</v>
+        <v>497272</v>
       </c>
       <c r="R32" t="n">
-        <v>6832737</v>
+        <v>6832783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476451</v>
+        <v>129476435</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497241</v>
+        <v>497301</v>
       </c>
       <c r="R33" t="n">
-        <v>6832763</v>
+        <v>6832764</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476452</v>
+        <v>129476466</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497258</v>
+        <v>497385</v>
       </c>
       <c r="R34" t="n">
-        <v>6832721</v>
+        <v>6832779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476466</v>
+        <v>129476451</v>
       </c>
       <c r="B35" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497385</v>
+        <v>497241</v>
       </c>
       <c r="R35" t="n">
-        <v>6832779</v>
+        <v>6832763</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476435</v>
+        <v>129476452</v>
       </c>
       <c r="B36" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497301</v>
+        <v>497258</v>
       </c>
       <c r="R36" t="n">
-        <v>6832764</v>
+        <v>6832721</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4770,45 +4770,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476424</v>
+        <v>129465323</v>
       </c>
       <c r="B44" t="n">
-        <v>97395</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497389</v>
+        <v>497290</v>
       </c>
       <c r="R44" t="n">
-        <v>6832716</v>
+        <v>6832699</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,22 +4855,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476433</v>
+        <v>129476421</v>
       </c>
       <c r="B45" t="n">
-        <v>91646</v>
+        <v>90625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497349</v>
+        <v>497336</v>
       </c>
       <c r="R45" t="n">
-        <v>6832759</v>
+        <v>6832758</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476421</v>
+        <v>129476422</v>
       </c>
       <c r="B46" t="n">
         <v>90625</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497336</v>
+        <v>497310</v>
       </c>
       <c r="R46" t="n">
-        <v>6832758</v>
+        <v>6832692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476422</v>
+        <v>129476424</v>
       </c>
       <c r="B47" t="n">
-        <v>90625</v>
+        <v>97395</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1962</v>
+        <v>2569</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497310</v>
+        <v>497389</v>
       </c>
       <c r="R47" t="n">
-        <v>6832692</v>
+        <v>6832716</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129465323</v>
+        <v>129476433</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91646</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497290</v>
+        <v>497349</v>
       </c>
       <c r="R48" t="n">
-        <v>6832699</v>
+        <v>6832759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,12 +5243,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476434</v>
+        <v>129476439</v>
       </c>
       <c r="B54" t="n">
-        <v>91646</v>
+        <v>78839</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497367</v>
+        <v>497415</v>
       </c>
       <c r="R54" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476465</v>
+        <v>129476434</v>
       </c>
       <c r="B55" t="n">
-        <v>78747</v>
+        <v>91646</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497434</v>
+        <v>497367</v>
       </c>
       <c r="R55" t="n">
-        <v>6832759</v>
+        <v>6832720</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,10 +6225,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476439</v>
+        <v>129476465</v>
       </c>
       <c r="B59" t="n">
-        <v>78839</v>
+        <v>78747</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,21 +6236,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497415</v>
+        <v>497434</v>
       </c>
       <c r="R59" t="n">
-        <v>6832767</v>
+        <v>6832759</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129466545</v>
+        <v>129476432</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>91646</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497366</v>
+        <v>497389</v>
       </c>
       <c r="R63" t="n">
-        <v>6832752</v>
+        <v>6832749</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,19 +6698,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129465171</v>
+        <v>129466545</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497309</v>
+        <v>497366</v>
       </c>
       <c r="R64" t="n">
-        <v>6832672</v>
+        <v>6832752</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129476432</v>
+        <v>129465171</v>
       </c>
       <c r="B65" t="n">
-        <v>91646</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497389</v>
+        <v>497309</v>
       </c>
       <c r="R65" t="n">
-        <v>6832749</v>
+        <v>6832672</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,57 +6892,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129476431</v>
+        <v>129464850</v>
       </c>
       <c r="B66" t="n">
-        <v>92236</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497392</v>
+        <v>497345</v>
       </c>
       <c r="R66" t="n">
-        <v>6832754</v>
+        <v>6832696</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,57 +6989,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464850</v>
+        <v>129476431</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>92236</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497345</v>
+        <v>497392</v>
       </c>
       <c r="R67" t="n">
-        <v>6832696</v>
+        <v>6832754</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,12 +7086,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B9" t="n">
-        <v>90625</v>
+        <v>78838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,34 +1378,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R9" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,12 +1452,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B11" t="n">
-        <v>78838</v>
+        <v>90629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,44 +1646,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476426</v>
+        <v>129476428</v>
       </c>
       <c r="B12" t="n">
-        <v>97395</v>
+        <v>92883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497413</v>
+        <v>497387</v>
       </c>
       <c r="R12" t="n">
-        <v>6832724</v>
+        <v>6832781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476423</v>
+        <v>129476464</v>
       </c>
       <c r="B13" t="n">
-        <v>97395</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497256</v>
+        <v>497336</v>
       </c>
       <c r="R13" t="n">
-        <v>6832740</v>
+        <v>6832724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476427</v>
+        <v>129476462</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>78747</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,42 +1863,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497307</v>
+        <v>497254</v>
       </c>
       <c r="R14" t="n">
-        <v>6832769</v>
+        <v>6832752</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,10 +1949,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476464</v>
+        <v>129476427</v>
       </c>
       <c r="B15" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,34 +1960,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497336</v>
+        <v>497307</v>
       </c>
       <c r="R15" t="n">
-        <v>6832724</v>
+        <v>6832769</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476462</v>
+        <v>129465572</v>
       </c>
       <c r="B16" t="n">
-        <v>78747</v>
+        <v>80186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,34 +2065,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832752</v>
+        <v>6832729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,44 +2139,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476428</v>
+        <v>129476423</v>
       </c>
       <c r="B17" t="n">
-        <v>92879</v>
+        <v>97399</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497387</v>
+        <v>497256</v>
       </c>
       <c r="R17" t="n">
-        <v>6832781</v>
+        <v>6832740</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,45 +2248,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129465572</v>
+        <v>129476426</v>
       </c>
       <c r="B18" t="n">
-        <v>80186</v>
+        <v>97399</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497254</v>
+        <v>497413</v>
       </c>
       <c r="R18" t="n">
-        <v>6832729</v>
+        <v>6832724</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,12 +2333,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476417</v>
+        <v>129464639</v>
       </c>
       <c r="B25" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,34 +2938,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497430</v>
+        <v>497352</v>
       </c>
       <c r="R25" t="n">
-        <v>6832760</v>
+        <v>6832732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,44 +3012,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476446</v>
+        <v>129476454</v>
       </c>
       <c r="B26" t="n">
-        <v>91766</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497331</v>
+        <v>497292</v>
       </c>
       <c r="R26" t="n">
-        <v>6832758</v>
+        <v>6832702</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129464639</v>
+        <v>129476417</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3132,34 +3132,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497352</v>
+        <v>497430</v>
       </c>
       <c r="R27" t="n">
-        <v>6832732</v>
+        <v>6832760</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,44 +3206,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476454</v>
+        <v>129476446</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>91770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497292</v>
+        <v>497331</v>
       </c>
       <c r="R28" t="n">
-        <v>6832702</v>
+        <v>6832758</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476430</v>
+        <v>129476450</v>
       </c>
       <c r="B30" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497250</v>
+        <v>497272</v>
       </c>
       <c r="R30" t="n">
-        <v>6832730</v>
+        <v>6832783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476450</v>
+        <v>129476430</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497272</v>
+        <v>497250</v>
       </c>
       <c r="R32" t="n">
-        <v>6832783</v>
+        <v>6832730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476435</v>
+        <v>129476466</v>
       </c>
       <c r="B33" t="n">
-        <v>78839</v>
+        <v>92879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497301</v>
+        <v>497385</v>
       </c>
       <c r="R33" t="n">
-        <v>6832764</v>
+        <v>6832779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476466</v>
+        <v>129476451</v>
       </c>
       <c r="B34" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497385</v>
+        <v>497241</v>
       </c>
       <c r="R34" t="n">
-        <v>6832779</v>
+        <v>6832763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476451</v>
+        <v>129476452</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497241</v>
+        <v>497258</v>
       </c>
       <c r="R35" t="n">
-        <v>6832763</v>
+        <v>6832721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476452</v>
+        <v>129476435</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497258</v>
+        <v>497301</v>
       </c>
       <c r="R36" t="n">
-        <v>6832721</v>
+        <v>6832764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476455</v>
+        <v>129476436</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497307</v>
+        <v>497334</v>
       </c>
       <c r="R39" t="n">
-        <v>6832696</v>
+        <v>6832674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476436</v>
+        <v>129476455</v>
       </c>
       <c r="B40" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497334</v>
+        <v>497307</v>
       </c>
       <c r="R40" t="n">
-        <v>6832674</v>
+        <v>6832696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R41" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,22 +4564,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476443</v>
+        <v>129464008</v>
       </c>
       <c r="B42" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497393</v>
+        <v>497425</v>
       </c>
       <c r="R42" t="n">
-        <v>6832735</v>
+        <v>6832750</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,12 +4661,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4867,32 +4867,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476421</v>
+        <v>129476424</v>
       </c>
       <c r="B45" t="n">
-        <v>90625</v>
+        <v>97399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>2569</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497336</v>
+        <v>497389</v>
       </c>
       <c r="R45" t="n">
-        <v>6832758</v>
+        <v>6832716</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4967,7 +4967,7 @@
         <v>129476422</v>
       </c>
       <c r="B46" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,32 +5061,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476424</v>
+        <v>129476421</v>
       </c>
       <c r="B47" t="n">
-        <v>97395</v>
+        <v>90629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2569</v>
+        <v>1962</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497389</v>
+        <v>497336</v>
       </c>
       <c r="R47" t="n">
-        <v>6832716</v>
+        <v>6832758</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5161,7 +5161,7 @@
         <v>129476433</v>
       </c>
       <c r="B48" t="n">
-        <v>91646</v>
+        <v>91650</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476439</v>
+        <v>129476434</v>
       </c>
       <c r="B54" t="n">
-        <v>78839</v>
+        <v>91650</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497415</v>
+        <v>497367</v>
       </c>
       <c r="R54" t="n">
-        <v>6832767</v>
+        <v>6832720</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476434</v>
+        <v>129476465</v>
       </c>
       <c r="B55" t="n">
-        <v>91646</v>
+        <v>78747</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497367</v>
+        <v>497434</v>
       </c>
       <c r="R55" t="n">
-        <v>6832720</v>
+        <v>6832759</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,10 +6225,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476465</v>
+        <v>129476439</v>
       </c>
       <c r="B59" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,21 +6236,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497434</v>
+        <v>497415</v>
       </c>
       <c r="R59" t="n">
-        <v>6832759</v>
+        <v>6832767</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476432</v>
+        <v>129466545</v>
       </c>
       <c r="B63" t="n">
-        <v>91646</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6624,34 +6624,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497389</v>
+        <v>497366</v>
       </c>
       <c r="R63" t="n">
-        <v>6832749</v>
+        <v>6832752</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6698,19 +6698,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129466545</v>
+        <v>129465171</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497366</v>
+        <v>497309</v>
       </c>
       <c r="R64" t="n">
-        <v>6832752</v>
+        <v>6832672</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129465171</v>
+        <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>91650</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,34 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497309</v>
+        <v>497389</v>
       </c>
       <c r="R65" t="n">
-        <v>6832672</v>
+        <v>6832749</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,57 +6892,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464850</v>
+        <v>129476431</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>92240</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497345</v>
+        <v>497392</v>
       </c>
       <c r="R66" t="n">
-        <v>6832696</v>
+        <v>6832754</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,57 +6989,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129476431</v>
+        <v>129464850</v>
       </c>
       <c r="B67" t="n">
-        <v>92236</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497392</v>
+        <v>497345</v>
       </c>
       <c r="R67" t="n">
-        <v>6832754</v>
+        <v>6832696</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,12 +7086,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129465376</v>
+        <v>129476418</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497292</v>
+        <v>497415</v>
       </c>
       <c r="R6" t="n">
-        <v>6832709</v>
+        <v>6832767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1161,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476453</v>
+        <v>129465376</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1204,14 +1204,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497266</v>
+        <v>497292</v>
       </c>
       <c r="R7" t="n">
-        <v>6832713</v>
+        <v>6832709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476418</v>
+        <v>129476453</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497415</v>
+        <v>497266</v>
       </c>
       <c r="R8" t="n">
-        <v>6832767</v>
+        <v>6832713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129476442</v>
+        <v>129464751</v>
       </c>
       <c r="B9" t="n">
-        <v>78838</v>
+        <v>90631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,34 +1378,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497337</v>
+        <v>497356</v>
       </c>
       <c r="R9" t="n">
-        <v>6832676</v>
+        <v>6832723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,12 +1452,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129464751</v>
+        <v>129476442</v>
       </c>
       <c r="B11" t="n">
-        <v>90629</v>
+        <v>78838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R11" t="n">
-        <v>6832723</v>
+        <v>6832676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,44 +1646,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476428</v>
+        <v>129476426</v>
       </c>
       <c r="B12" t="n">
-        <v>92883</v>
+        <v>97401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497387</v>
+        <v>497413</v>
       </c>
       <c r="R12" t="n">
-        <v>6832781</v>
+        <v>6832724</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476464</v>
+        <v>129476423</v>
       </c>
       <c r="B13" t="n">
-        <v>78747</v>
+        <v>97401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497336</v>
+        <v>497256</v>
       </c>
       <c r="R13" t="n">
-        <v>6832724</v>
+        <v>6832740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476462</v>
+        <v>129476419</v>
       </c>
       <c r="B14" t="n">
-        <v>78747</v>
+        <v>79671</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497254</v>
+        <v>497336</v>
       </c>
       <c r="R14" t="n">
-        <v>6832752</v>
+        <v>6832679</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476427</v>
+        <v>129476464</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>78747</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,42 +1960,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497307</v>
+        <v>497336</v>
       </c>
       <c r="R15" t="n">
-        <v>6832769</v>
+        <v>6832724</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129465572</v>
+        <v>129476462</v>
       </c>
       <c r="B16" t="n">
-        <v>80186</v>
+        <v>78747</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,34 +2057,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>497254</v>
       </c>
       <c r="R16" t="n">
-        <v>6832729</v>
+        <v>6832752</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,44 +2131,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476423</v>
+        <v>129476428</v>
       </c>
       <c r="B17" t="n">
-        <v>97399</v>
+        <v>92885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2186,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497256</v>
+        <v>497387</v>
       </c>
       <c r="R17" t="n">
-        <v>6832740</v>
+        <v>6832781</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,45 +2240,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476426</v>
+        <v>129465572</v>
       </c>
       <c r="B18" t="n">
-        <v>97399</v>
+        <v>80186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497413</v>
+        <v>497254</v>
       </c>
       <c r="R18" t="n">
-        <v>6832724</v>
+        <v>6832729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,22 +2325,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476419</v>
+        <v>129476427</v>
       </c>
       <c r="B19" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2356,34 +2348,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497336</v>
+        <v>497307</v>
       </c>
       <c r="R19" t="n">
-        <v>6832679</v>
+        <v>6832769</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129464182</v>
+        <v>129476437</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497410</v>
+        <v>497395</v>
       </c>
       <c r="R22" t="n">
-        <v>6832744</v>
+        <v>6832737</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,12 +2721,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476437</v>
+        <v>129464182</v>
       </c>
       <c r="B24" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,34 +2841,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497395</v>
+        <v>497410</v>
       </c>
       <c r="R24" t="n">
-        <v>6832737</v>
+        <v>6832744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,57 +2915,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129464639</v>
+        <v>129476446</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>91772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497352</v>
+        <v>497331</v>
       </c>
       <c r="R25" t="n">
-        <v>6832732</v>
+        <v>6832758</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,19 +3012,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476454</v>
+        <v>129464639</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3055,14 +3055,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497292</v>
+        <v>497352</v>
       </c>
       <c r="R26" t="n">
-        <v>6832702</v>
+        <v>6832732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,12 +3109,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476446</v>
+        <v>129476454</v>
       </c>
       <c r="B28" t="n">
-        <v>91770</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497331</v>
+        <v>497292</v>
       </c>
       <c r="R28" t="n">
-        <v>6832758</v>
+        <v>6832702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476450</v>
+        <v>129476430</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497272</v>
+        <v>497250</v>
       </c>
       <c r="R30" t="n">
-        <v>6832783</v>
+        <v>6832730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476416</v>
+        <v>129476450</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497395</v>
+        <v>497272</v>
       </c>
       <c r="R31" t="n">
-        <v>6832737</v>
+        <v>6832783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476430</v>
+        <v>129476416</v>
       </c>
       <c r="B32" t="n">
-        <v>80187</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497250</v>
+        <v>497395</v>
       </c>
       <c r="R32" t="n">
-        <v>6832730</v>
+        <v>6832737</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476466</v>
+        <v>129476451</v>
       </c>
       <c r="B33" t="n">
-        <v>92879</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497385</v>
+        <v>497241</v>
       </c>
       <c r="R33" t="n">
-        <v>6832779</v>
+        <v>6832763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476451</v>
+        <v>129476452</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497241</v>
+        <v>497258</v>
       </c>
       <c r="R34" t="n">
-        <v>6832763</v>
+        <v>6832721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476452</v>
+        <v>129476466</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497258</v>
+        <v>497385</v>
       </c>
       <c r="R35" t="n">
-        <v>6832721</v>
+        <v>6832779</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476443</v>
+        <v>129464008</v>
       </c>
       <c r="B41" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4490,34 +4490,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497393</v>
+        <v>497425</v>
       </c>
       <c r="R41" t="n">
-        <v>6832735</v>
+        <v>6832750</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,22 +4564,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129464008</v>
+        <v>129476443</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497425</v>
+        <v>497393</v>
       </c>
       <c r="R42" t="n">
-        <v>6832750</v>
+        <v>6832735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4661,12 +4661,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129465323</v>
+        <v>129476421</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>90631</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497290</v>
+        <v>497336</v>
       </c>
       <c r="R44" t="n">
-        <v>6832699</v>
+        <v>6832758</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4855,44 +4855,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476424</v>
+        <v>129476422</v>
       </c>
       <c r="B45" t="n">
-        <v>97399</v>
+        <v>90631</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2569</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497389</v>
+        <v>497310</v>
       </c>
       <c r="R45" t="n">
-        <v>6832716</v>
+        <v>6832692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476422</v>
+        <v>129476433</v>
       </c>
       <c r="B46" t="n">
-        <v>90629</v>
+        <v>91652</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497310</v>
+        <v>497349</v>
       </c>
       <c r="R46" t="n">
-        <v>6832692</v>
+        <v>6832759</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476421</v>
+        <v>129465323</v>
       </c>
       <c r="B47" t="n">
-        <v>90629</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497336</v>
+        <v>497290</v>
       </c>
       <c r="R47" t="n">
-        <v>6832758</v>
+        <v>6832699</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5146,44 +5146,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476433</v>
+        <v>129476424</v>
       </c>
       <c r="B48" t="n">
-        <v>91650</v>
+        <v>97401</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>2569</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497349</v>
+        <v>497389</v>
       </c>
       <c r="R48" t="n">
-        <v>6832759</v>
+        <v>6832716</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B50" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R50" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B51" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R51" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476460</v>
+        <v>129476461</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497427</v>
+        <v>497297</v>
       </c>
       <c r="R52" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R53" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476434</v>
+        <v>129476465</v>
       </c>
       <c r="B54" t="n">
-        <v>91650</v>
+        <v>78747</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497367</v>
+        <v>497434</v>
       </c>
       <c r="R54" t="n">
-        <v>6832720</v>
+        <v>6832759</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476465</v>
+        <v>129476434</v>
       </c>
       <c r="B55" t="n">
-        <v>78747</v>
+        <v>91652</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497434</v>
+        <v>497367</v>
       </c>
       <c r="R55" t="n">
-        <v>6832759</v>
+        <v>6832720</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>129476432</v>
       </c>
       <c r="B65" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>129476431</v>
       </c>
       <c r="B66" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476437</v>
+        <v>129464182</v>
       </c>
       <c r="B22" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,34 +2647,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497395</v>
+        <v>497410</v>
       </c>
       <c r="R22" t="n">
-        <v>6832737</v>
+        <v>6832744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,12 +2721,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129464182</v>
+        <v>129476437</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,34 +2841,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497410</v>
+        <v>497395</v>
       </c>
       <c r="R24" t="n">
-        <v>6832744</v>
+        <v>6832737</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,12 +2915,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476460</v>
+        <v>129476461</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497427</v>
+        <v>497297</v>
       </c>
       <c r="R50" t="n">
-        <v>6832743</v>
+        <v>6832767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476456</v>
+        <v>129476463</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497344</v>
+        <v>497356</v>
       </c>
       <c r="R51" t="n">
-        <v>6832689</v>
+        <v>6832686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B52" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R52" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476463</v>
+        <v>129476456</v>
       </c>
       <c r="B53" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497356</v>
+        <v>497344</v>
       </c>
       <c r="R53" t="n">
-        <v>6832686</v>
+        <v>6832689</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6904,45 +6904,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129476431</v>
+        <v>129465586</v>
       </c>
       <c r="B66" t="n">
-        <v>92242</v>
+        <v>57896</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>483</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497392</v>
+        <v>497254</v>
       </c>
       <c r="R66" t="n">
-        <v>6832754</v>
+        <v>6832729</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,22 +6989,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464850</v>
+        <v>129476420</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497345</v>
+        <v>497431</v>
       </c>
       <c r="R67" t="n">
-        <v>6832696</v>
+        <v>6832752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,57 +7086,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129465586</v>
+        <v>129476431</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>92242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>483</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497254</v>
+        <v>497392</v>
       </c>
       <c r="R68" t="n">
-        <v>6832729</v>
+        <v>6832754</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129476420</v>
+        <v>129464850</v>
       </c>
       <c r="B69" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497431</v>
+        <v>497345</v>
       </c>
       <c r="R69" t="n">
-        <v>6832752</v>
+        <v>6832696</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476466</v>
+        <v>129476435</v>
       </c>
       <c r="B35" t="n">
-        <v>92881</v>
+        <v>78839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497385</v>
+        <v>497301</v>
       </c>
       <c r="R35" t="n">
-        <v>6832779</v>
+        <v>6832764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476435</v>
+        <v>129476466</v>
       </c>
       <c r="B36" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497301</v>
+        <v>497385</v>
       </c>
       <c r="R36" t="n">
-        <v>6832764</v>
+        <v>6832779</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476465</v>
+        <v>129476439</v>
       </c>
       <c r="B54" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497434</v>
+        <v>497415</v>
       </c>
       <c r="R54" t="n">
-        <v>6832759</v>
+        <v>6832767</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476434</v>
+        <v>129476465</v>
       </c>
       <c r="B55" t="n">
-        <v>91652</v>
+        <v>78747</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497367</v>
+        <v>497434</v>
       </c>
       <c r="R55" t="n">
-        <v>6832720</v>
+        <v>6832759</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129464078</v>
+        <v>129476434</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>91652</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,34 +5945,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497426</v>
+        <v>497367</v>
       </c>
       <c r="R56" t="n">
-        <v>6832743</v>
+        <v>6832720</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6019,19 +6019,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129466317</v>
+        <v>129464078</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497335</v>
+        <v>497426</v>
       </c>
       <c r="R57" t="n">
-        <v>6832765</v>
+        <v>6832743</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129463331</v>
+        <v>129466317</v>
       </c>
       <c r="B58" t="n">
-        <v>58171</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6139,21 +6139,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102999</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497447</v>
+        <v>497335</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6832765</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6225,10 +6225,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476439</v>
+        <v>129463331</v>
       </c>
       <c r="B59" t="n">
-        <v>78839</v>
+        <v>58171</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,37 +6236,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>102999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497415</v>
+        <v>497447</v>
       </c>
       <c r="R59" t="n">
         <v>6832767</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6310,12 +6310,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -6904,45 +6904,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129465586</v>
+        <v>129476431</v>
       </c>
       <c r="B66" t="n">
-        <v>57896</v>
+        <v>92242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>483</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497254</v>
+        <v>497392</v>
       </c>
       <c r="R66" t="n">
-        <v>6832729</v>
+        <v>6832754</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,22 +6989,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129476420</v>
+        <v>129464850</v>
       </c>
       <c r="B67" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497431</v>
+        <v>497345</v>
       </c>
       <c r="R67" t="n">
-        <v>6832752</v>
+        <v>6832696</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,57 +7086,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129476431</v>
+        <v>129465586</v>
       </c>
       <c r="B68" t="n">
-        <v>92242</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>483</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497392</v>
+        <v>497254</v>
       </c>
       <c r="R68" t="n">
-        <v>6832754</v>
+        <v>6832729</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129464850</v>
+        <v>129476420</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7206,34 +7206,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497345</v>
+        <v>497431</v>
       </c>
       <c r="R69" t="n">
-        <v>6832696</v>
+        <v>6832752</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7280,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126279522</v>
+        <v>129464293</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497437</v>
+        <v>497396</v>
       </c>
       <c r="R2" t="n">
-        <v>6833130</v>
+        <v>6832740</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126279620</v>
+        <v>129476461</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497522</v>
+        <v>497297</v>
       </c>
       <c r="R3" t="n">
-        <v>6833149</v>
+        <v>6832767</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,64 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126279534</v>
+        <v>129476462</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497561</v>
+        <v>497254</v>
       </c>
       <c r="R4" t="n">
-        <v>6833164</v>
+        <v>6832752</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -938,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -958,69 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126279646</v>
+        <v>129476463</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497517</v>
+        <v>497356</v>
       </c>
       <c r="R5" t="n">
-        <v>6833161</v>
+        <v>6832686</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129476418</v>
+        <v>129476464</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497415</v>
+        <v>497336</v>
       </c>
       <c r="R6" t="n">
-        <v>6832767</v>
+        <v>6832724</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129465376</v>
+        <v>129476465</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497292</v>
+        <v>497434</v>
       </c>
       <c r="R7" t="n">
-        <v>6832709</v>
+        <v>6832759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476453</v>
+        <v>129476431</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>92557</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497266</v>
+        <v>497392</v>
       </c>
       <c r="R8" t="n">
-        <v>6832713</v>
+        <v>6832754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129464751</v>
+        <v>129476446</v>
       </c>
       <c r="B9" t="n">
-        <v>90631</v>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497356</v>
+        <v>497331</v>
       </c>
       <c r="R9" t="n">
-        <v>6832723</v>
+        <v>6832758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129467135</v>
+        <v>129464751</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497389</v>
+        <v>497356</v>
       </c>
       <c r="R10" t="n">
-        <v>6832791</v>
+        <v>6832723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476442</v>
+        <v>129476421</v>
       </c>
       <c r="B11" t="n">
-        <v>78838</v>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497337</v>
+        <v>497336</v>
       </c>
       <c r="R11" t="n">
-        <v>6832676</v>
+        <v>6832758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476426</v>
+        <v>129476422</v>
       </c>
       <c r="B12" t="n">
-        <v>97401</v>
+        <v>90932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497413</v>
+        <v>497310</v>
       </c>
       <c r="R12" t="n">
-        <v>6832724</v>
+        <v>6832692</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476423</v>
+        <v>129476432</v>
       </c>
       <c r="B13" t="n">
-        <v>97401</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497256</v>
+        <v>497389</v>
       </c>
       <c r="R13" t="n">
-        <v>6832740</v>
+        <v>6832749</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476419</v>
+        <v>129476433</v>
       </c>
       <c r="B14" t="n">
-        <v>79671</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497336</v>
+        <v>497349</v>
       </c>
       <c r="R14" t="n">
-        <v>6832679</v>
+        <v>6832759</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476464</v>
+        <v>129476434</v>
       </c>
       <c r="B15" t="n">
-        <v>78747</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1984,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497336</v>
+        <v>497367</v>
       </c>
       <c r="R15" t="n">
-        <v>6832724</v>
+        <v>6832720</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476462</v>
+        <v>129476429</v>
       </c>
       <c r="B16" t="n">
-        <v>78747</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497254</v>
+        <v>497288</v>
       </c>
       <c r="R16" t="n">
-        <v>6832752</v>
+        <v>6832771</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476428</v>
+        <v>129476430</v>
       </c>
       <c r="B17" t="n">
-        <v>92885</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497387</v>
+        <v>497250</v>
       </c>
       <c r="R17" t="n">
-        <v>6832781</v>
+        <v>6832730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,45 +2227,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129465572</v>
+        <v>129476423</v>
       </c>
       <c r="B18" t="n">
-        <v>80186</v>
+        <v>97733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497254</v>
+        <v>497256</v>
       </c>
       <c r="R18" t="n">
-        <v>6832729</v>
+        <v>6832740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2325,65 +2312,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476427</v>
+        <v>129476424</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>97733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497307</v>
+        <v>497389</v>
       </c>
       <c r="R19" t="n">
-        <v>6832769</v>
+        <v>6832716</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476449</v>
+        <v>129476426</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>97733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2477,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497318</v>
+        <v>497413</v>
       </c>
       <c r="R20" t="n">
-        <v>6832776</v>
+        <v>6832724</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2539,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476457</v>
+        <v>129476466</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497355</v>
+        <v>497385</v>
       </c>
       <c r="R21" t="n">
-        <v>6832689</v>
+        <v>6832779</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,45 +2615,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129464182</v>
+        <v>129476428</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>93201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497410</v>
+        <v>497387</v>
       </c>
       <c r="R22" t="n">
-        <v>6832744</v>
+        <v>6832781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,44 +2700,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476429</v>
+        <v>126279522</v>
       </c>
       <c r="B23" t="n">
-        <v>80187</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,13 +2747,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497288</v>
+        <v>497437</v>
       </c>
       <c r="R23" t="n">
-        <v>6832771</v>
+        <v>6833130</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2798,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2818,57 +2797,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476437</v>
+        <v>129464008</v>
       </c>
       <c r="B24" t="n">
-        <v>78839</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497395</v>
+        <v>497425</v>
       </c>
       <c r="R24" t="n">
-        <v>6832737</v>
+        <v>6832750</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,22 +2894,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476446</v>
+        <v>129464078</v>
       </c>
       <c r="B25" t="n">
-        <v>91772</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,34 +2917,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497331</v>
+        <v>497426</v>
       </c>
       <c r="R25" t="n">
-        <v>6832758</v>
+        <v>6832743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,26 +2991,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129464639</v>
+        <v>129464182</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3059,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497352</v>
+        <v>497410</v>
       </c>
       <c r="R26" t="n">
-        <v>6832732</v>
+        <v>6832744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,45 +3100,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476417</v>
+        <v>129464639</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497430</v>
+        <v>497352</v>
       </c>
       <c r="R27" t="n">
-        <v>6832760</v>
+        <v>6832732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,26 +3185,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476454</v>
+        <v>129464850</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3249,14 +3228,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497292</v>
+        <v>497345</v>
       </c>
       <c r="R28" t="n">
-        <v>6832702</v>
+        <v>6832696</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3303,44 +3282,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129464293</v>
+        <v>129464883</v>
       </c>
       <c r="B29" t="n">
-        <v>78747</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,13 +3329,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497396</v>
+        <v>497348</v>
       </c>
       <c r="R29" t="n">
-        <v>6832740</v>
+        <v>6832675</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3412,45 +3391,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476430</v>
+        <v>129465171</v>
       </c>
       <c r="B30" t="n">
-        <v>80187</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497250</v>
+        <v>497309</v>
       </c>
       <c r="R30" t="n">
-        <v>6832730</v>
+        <v>6832672</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3497,26 +3476,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476450</v>
+        <v>129465323</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3540,14 +3519,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497272</v>
+        <v>497290</v>
       </c>
       <c r="R31" t="n">
-        <v>6832783</v>
+        <v>6832699</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3594,57 +3573,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476416</v>
+        <v>129465376</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497395</v>
+        <v>497292</v>
       </c>
       <c r="R32" t="n">
-        <v>6832737</v>
+        <v>6832709</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3691,26 +3670,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476451</v>
+        <v>129465773</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3734,14 +3713,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497241</v>
+        <v>497256</v>
       </c>
       <c r="R33" t="n">
-        <v>6832763</v>
+        <v>6832783</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3788,26 +3767,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476452</v>
+        <v>129466317</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3831,14 +3810,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497258</v>
+        <v>497335</v>
       </c>
       <c r="R34" t="n">
-        <v>6832721</v>
+        <v>6832765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,57 +3864,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476435</v>
+        <v>129466545</v>
       </c>
       <c r="B35" t="n">
-        <v>78839</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497301</v>
+        <v>497366</v>
       </c>
       <c r="R35" t="n">
-        <v>6832764</v>
+        <v>6832752</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,57 +3961,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476466</v>
+        <v>129467135</v>
       </c>
       <c r="B36" t="n">
-        <v>92881</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497385</v>
+        <v>497389</v>
       </c>
       <c r="R36" t="n">
-        <v>6832779</v>
+        <v>6832791</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4079,26 +4058,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476459</v>
+        <v>129476447</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4126,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497362</v>
+        <v>497367</v>
       </c>
       <c r="R37" t="n">
-        <v>6832731</v>
+        <v>6832744</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,32 +4167,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476438</v>
+        <v>129476448</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4223,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497401</v>
+        <v>497361</v>
       </c>
       <c r="R38" t="n">
-        <v>6832738</v>
+        <v>6832760</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4285,32 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476436</v>
+        <v>129476449</v>
       </c>
       <c r="B39" t="n">
-        <v>78839</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4320,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497334</v>
+        <v>497318</v>
       </c>
       <c r="R39" t="n">
-        <v>6832674</v>
+        <v>6832776</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4382,14 +4361,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476455</v>
+        <v>129476450</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4417,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497307</v>
+        <v>497272</v>
       </c>
       <c r="R40" t="n">
-        <v>6832696</v>
+        <v>6832783</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4479,14 +4458,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129464008</v>
+        <v>129476451</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4510,14 +4489,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497425</v>
+        <v>497241</v>
       </c>
       <c r="R41" t="n">
-        <v>6832750</v>
+        <v>6832763</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4564,44 +4543,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476443</v>
+        <v>129476452</v>
       </c>
       <c r="B42" t="n">
-        <v>78838</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4611,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497393</v>
+        <v>497258</v>
       </c>
       <c r="R42" t="n">
-        <v>6832735</v>
+        <v>6832721</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4673,14 +4652,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129465773</v>
+        <v>129476453</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4704,14 +4683,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497256</v>
+        <v>497266</v>
       </c>
       <c r="R43" t="n">
-        <v>6832783</v>
+        <v>6832713</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4758,44 +4737,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476421</v>
+        <v>129476454</v>
       </c>
       <c r="B44" t="n">
-        <v>90631</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4805,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497336</v>
+        <v>497292</v>
       </c>
       <c r="R44" t="n">
-        <v>6832758</v>
+        <v>6832702</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4867,32 +4846,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476422</v>
+        <v>129476455</v>
       </c>
       <c r="B45" t="n">
-        <v>90631</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4902,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497310</v>
+        <v>497307</v>
       </c>
       <c r="R45" t="n">
-        <v>6832692</v>
+        <v>6832696</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4964,32 +4943,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476433</v>
+        <v>129476456</v>
       </c>
       <c r="B46" t="n">
-        <v>91652</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4999,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497349</v>
+        <v>497344</v>
       </c>
       <c r="R46" t="n">
-        <v>6832759</v>
+        <v>6832689</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,14 +5040,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129465323</v>
+        <v>129476457</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5092,14 +5071,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497290</v>
+        <v>497355</v>
       </c>
       <c r="R47" t="n">
-        <v>6832699</v>
+        <v>6832689</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5146,44 +5125,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476424</v>
+        <v>129476458</v>
       </c>
       <c r="B48" t="n">
-        <v>97401</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5193,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497389</v>
+        <v>497334</v>
       </c>
       <c r="R48" t="n">
-        <v>6832716</v>
+        <v>6832718</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5255,32 +5234,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476415</v>
+        <v>129476459</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5290,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497337</v>
+        <v>497362</v>
       </c>
       <c r="R49" t="n">
-        <v>6832679</v>
+        <v>6832731</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5352,32 +5331,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476461</v>
+        <v>129476460</v>
       </c>
       <c r="B50" t="n">
-        <v>78747</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5387,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497297</v>
+        <v>497427</v>
       </c>
       <c r="R50" t="n">
-        <v>6832767</v>
+        <v>6832743</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,10 +5428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476463</v>
+        <v>129476442</v>
       </c>
       <c r="B51" t="n">
-        <v>78747</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5460,21 +5439,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5484,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497356</v>
+        <v>497337</v>
       </c>
       <c r="R51" t="n">
-        <v>6832686</v>
+        <v>6832676</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,10 +5525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476460</v>
+        <v>129476443</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5557,21 +5536,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5581,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497427</v>
+        <v>497393</v>
       </c>
       <c r="R52" t="n">
-        <v>6832743</v>
+        <v>6832735</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,10 +5622,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476456</v>
+        <v>129476415</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5654,21 +5633,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5678,10 +5657,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497344</v>
+        <v>497337</v>
       </c>
       <c r="R53" t="n">
-        <v>6832689</v>
+        <v>6832679</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,10 +5719,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476439</v>
+        <v>129476416</v>
       </c>
       <c r="B54" t="n">
-        <v>78839</v>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5751,21 +5730,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5775,10 +5754,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497415</v>
+        <v>497395</v>
       </c>
       <c r="R54" t="n">
-        <v>6832767</v>
+        <v>6832737</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5837,10 +5816,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476465</v>
+        <v>129476417</v>
       </c>
       <c r="B55" t="n">
-        <v>78747</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5848,21 +5827,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5872,10 +5851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497434</v>
+        <v>497430</v>
       </c>
       <c r="R55" t="n">
-        <v>6832759</v>
+        <v>6832760</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5934,10 +5913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476434</v>
+        <v>129476418</v>
       </c>
       <c r="B56" t="n">
-        <v>91652</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5945,21 +5924,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5969,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497367</v>
+        <v>497415</v>
       </c>
       <c r="R56" t="n">
-        <v>6832720</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6031,10 +6010,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129464078</v>
+        <v>129465572</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6042,21 +6021,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6066,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497426</v>
+        <v>497254</v>
       </c>
       <c r="R57" t="n">
-        <v>6832743</v>
+        <v>6832729</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6128,45 +6107,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129466317</v>
+        <v>129476427</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497335</v>
+        <v>497307</v>
       </c>
       <c r="R58" t="n">
-        <v>6832765</v>
+        <v>6832769</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6213,22 +6200,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129463331</v>
+        <v>126279620</v>
       </c>
       <c r="B59" t="n">
-        <v>58171</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6236,34 +6223,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102999</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497447</v>
+        <v>497522</v>
       </c>
       <c r="R59" t="n">
-        <v>6832767</v>
+        <v>6833149</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6290,12 +6277,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6322,10 +6309,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476448</v>
+        <v>129463331</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>58393</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6333,37 +6320,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>102999</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497361</v>
+        <v>497447</v>
       </c>
       <c r="R60" t="n">
-        <v>6832760</v>
+        <v>6832767</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6407,22 +6394,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476458</v>
+        <v>129465586</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>58114</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6430,34 +6417,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497334</v>
+        <v>497254</v>
       </c>
       <c r="R61" t="n">
-        <v>6832718</v>
+        <v>6832729</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6504,60 +6491,64 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476447</v>
+        <v>126279534</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497367</v>
+        <v>497561</v>
       </c>
       <c r="R62" t="n">
-        <v>6832744</v>
+        <v>6833164</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6581,12 +6572,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6601,60 +6592,69 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129466545</v>
+        <v>126279646</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497366</v>
+        <v>497517</v>
       </c>
       <c r="R63" t="n">
-        <v>6832752</v>
+        <v>6833161</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6678,12 +6678,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6710,10 +6710,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129465171</v>
+        <v>129476435</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>79085</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6721,34 +6721,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497309</v>
+        <v>497301</v>
       </c>
       <c r="R64" t="n">
-        <v>6832672</v>
+        <v>6832764</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6795,22 +6795,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129476432</v>
+        <v>129476436</v>
       </c>
       <c r="B65" t="n">
-        <v>91652</v>
+        <v>79085</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497389</v>
+        <v>497334</v>
       </c>
       <c r="R65" t="n">
-        <v>6832749</v>
+        <v>6832674</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6904,32 +6904,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129476431</v>
+        <v>129476437</v>
       </c>
       <c r="B66" t="n">
-        <v>92242</v>
+        <v>79085</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>483</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497392</v>
+        <v>497395</v>
       </c>
       <c r="R66" t="n">
-        <v>6832754</v>
+        <v>6832737</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464850</v>
+        <v>129476438</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>79085</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7012,34 +7012,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497345</v>
+        <v>497401</v>
       </c>
       <c r="R67" t="n">
-        <v>6832696</v>
+        <v>6832738</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,22 +7086,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129465586</v>
+        <v>129476439</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>79085</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7109,34 +7109,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nälgojärvstjärnen, Nälgojärvstjärnen, Dlr</t>
+          <t>Nälgojärvstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497254</v>
+        <v>497415</v>
       </c>
       <c r="R68" t="n">
-        <v>6832729</v>
+        <v>6832767</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7183,22 +7183,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129476420</v>
+        <v>129476419</v>
       </c>
       <c r="B69" t="n">
-        <v>79671</v>
+        <v>79917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497431</v>
+        <v>497336</v>
       </c>
       <c r="R69" t="n">
-        <v>6832752</v>
+        <v>6832679</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7289,6 +7289,103 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129476420</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Nälgojärvstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>497431</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6832752</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 77-2025 artfynd.xlsx
+++ b/artfynd/A 77-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464293</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476461</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476462</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476463</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476465</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476431</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476446</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464751</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476421</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476422</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476432</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476433</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476434</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476429</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476430</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476423</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476424</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476426</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476466</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476428</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126279522</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464008</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464078</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464182</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464639</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464850</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464883</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465171</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465323</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465376</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465773</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466317</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466545</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129467135</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476447</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476448</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476449</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476450</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476451</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476452</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476453</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476454</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476455</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476456</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476457</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476458</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476459</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476460</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476442</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476443</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5716,6 +5976,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476415</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5813,6 +6078,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476416</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5910,6 +6180,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476417</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6007,6 +6282,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476418</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6104,6 +6384,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465572</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6209,6 +6494,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476427</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6306,6 +6596,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126279620</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6403,6 +6698,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129463331</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6500,6 +6800,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465586</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6601,6 +6906,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126279534</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6707,6 +7017,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126279646</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6804,6 +7119,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476435</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6901,6 +7221,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476436</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6998,6 +7323,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476437</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7095,6 +7425,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476438</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7192,6 +7527,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476439</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7289,6 +7629,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476419</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7386,8 +7731,84 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476420</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>